--- a/data/product-database/Longevity_Skincare_AI_Product_Database_v2_fill_template.xlsx
+++ b/data/product-database/Longevity_Skincare_AI_Product_Database_v2_fill_template.xlsx
@@ -25,8 +25,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="15">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
+  </numFmts>
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -108,8 +110,24 @@
       <color rgb="00C00000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -161,6 +179,26 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -193,7 +231,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -272,6 +310,48 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -736,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1070,6 +1150,73 @@
       <c r="B38" s="22" t="inlineStr">
         <is>
           <t>Nutrafol, Nordic Naturals ProOmega, HigherDOSE and ZIIP are supplements and devices. vAIne's MVP excludes supplements, peptides and prescriptions, so they arguably do not belong in this catalog at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="45" t="inlineStr">
+        <is>
+          <t>UPDATE 2026-09-04 — fragrance column populated, and the rule had to change</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="46" customHeight="1">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>45 of 81 rows now carry a verbatim published ingredient list, price and fragrance verdict, captured direct from brand pages.</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Young Goose 17, Alitura 10, Vitali 10, OneSkin 4, Revision 2, SkinBetter 2. 17 bundles and 4 not-found rows correctly left blank rather than filled by inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="46" customHeight="1">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>The naive rule would have been dangerous.</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Every single captured product passes the simple test — not one declares "Fragrance", "Parfum" or "Aroma". But 27 of 45 are built on essential oils. A user who selects "avoid fragrance" and is handed Angel's Mist (nine essential oils) has been failed by the data, not the app.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="46" customHeight="1">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>So Fragrance-Free = Yes requires BOTH conditions</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>(1) no Fragrance/Parfum/Aroma declared, AND (2) no essential oils or fragrant botanicals in the list. Where an essential oil is present the cell reads No, and the Allergen Flags column names the specific botanicals. The importer should treat this column as already reflecting that stricter test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="46" customHeight="1">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>Result: 18 Yes, 27 No, 36 still Unknown.</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>The Unknown rows are bundles (17), products not found (4), and brands whose sites blocked the fetch (12) — plus Alitura Clay Mask, which publishes no ingredient list at all despite claiming to be free of synthetic fragrance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="46" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
+          <t>Alitura has zero fragrance-free products.</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>All 10 captured Alitura items are essential-oil based; Santal Black is effectively a fragrance oil and contains Balsam of Peru, a well-known contact allergen. A fragrance-avoidant user can be shown nothing from this brand. Worth knowing, since Alitura is one of the three anchor brands.</t>
         </is>
       </c>
     </row>
@@ -1364,13 +1511,13 @@
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="15" customWidth="1" min="20" max="20"/>
     <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="46" customWidth="1" min="22" max="22"/>
+    <col width="60" customWidth="1" min="22" max="22"/>
     <col width="30" customWidth="1" min="23" max="23"/>
     <col width="17" customWidth="1" min="24" max="24"/>
     <col width="24" customWidth="1" min="25" max="25"/>
     <col width="20" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
-    <col width="22" customWidth="1" min="28" max="28"/>
+    <col width="34" customWidth="1" min="28" max="28"/>
     <col width="20" customWidth="1" min="29" max="29"/>
     <col width="52" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
@@ -1533,7 +1680,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
+    <row r="2" ht="58" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -1608,18 +1755,44 @@
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="11" t="n"/>
-      <c r="R2" s="11" t="n"/>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U2" s="11" t="n"/>
-      <c r="V2" s="11" t="n"/>
-      <c r="W2" s="11" t="n"/>
-      <c r="X2" s="11" t="n"/>
+      <c r="Q2" s="32" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="R2" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S2" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T2" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U2" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V2" s="36" t="inlineStr">
+        <is>
+          <t>Water, Glycerin, Isoprene Glycol, Resveratrol, CelVio Spermidine, Hydroxyethylcellulose, Palmitoyl Hexapeptide-12, Pentapeptide-18 (Leuphasyl), Tetrahexyldecyl Ascorbate, Hyaluronic Acid, Squalane, Panthenol, Camellia Sinensis (White Tea) Leaf Extract, Undecane, Tridecane, Pentaerythrityl Tetraisostearate, Caprylic/Capric Triglyceride, Stearalkonium Hectorite, Propylene Carbonate, Carbomer, Ergothioneine, Tricholoma Matsutake Mycelium Ferment Extract, Tricholoma Matsutake Extract, Ectoin, Nicotinamide Mononucleotide, Lavandula Angustifolia (French Lavender) Extract, Lonicera Caprifolium Flower Extract, Lonicera Japonica Flower Extract, Simmondsia Chinensis (Jojoba) Seed Oil, Citric Acid</t>
+        </is>
+      </c>
+      <c r="W2" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X2" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y2" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -1627,18 +1800,26 @@
       </c>
       <c r="Z2" s="11" t="n"/>
       <c r="AA2" s="11" t="n"/>
-      <c r="AB2" s="11" t="n"/>
+      <c r="AB2" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Lavender extract; white tea; honeysuckle; jojoba</t>
+        </is>
+      </c>
       <c r="AC2" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD2" s="15" t="n"/>
+      <c r="AD2" s="38" t="inlineStr">
+        <is>
+          <t>Full size $196.50 / travel $109</t>
+        </is>
+      </c>
       <c r="AE2" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="42" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>1</v>
       </c>
@@ -1713,18 +1894,44 @@
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="11" t="n"/>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="11" t="n"/>
-      <c r="T3" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U3" s="11" t="n"/>
-      <c r="V3" s="11" t="n"/>
-      <c r="W3" s="11" t="n"/>
-      <c r="X3" s="11" t="n"/>
+      <c r="Q3" s="32" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="R3" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S3" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T3" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U3" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V3" s="36" t="inlineStr">
+        <is>
+          <t>Water, Caprylic/Capric Triglyceride, Glycerine, Phenyl Trimethicone, Cetearyl Alcohol, Cetearyl Glucoside, Nicotinamide Mononucleotide, Resveratrol, CelVio Spermidine, Pentapeptide-18, Palmitoyl Hexapeptide-12, Tetrahexyldecyl Ascorbate, Squalane, Pentaerythrityl Tetraisostearate, Stearalkonium Hectorite, Propylene Carbonate, Ergothioneine, Tricholoma Matsutake Mycelium Ferment Extract, Tricholoma Matsutake Extract, Ectoin, Cera Alba (Beeswax), Isoprene Glycol, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Polyglyceryl-3 Distearate, Curcuma Longa (Turmeric) Root Extract, Hydroxyethylcellulose, Lonicera Caprifolium Flower Extract, Lonicera Japonica Flower Extract, Simmondsia Chinensis (Jojoba) Seed Oil, Disodium EDTA, Lavandula Angustifolia (French Lavender) Extract, Citric Acid</t>
+        </is>
+      </c>
+      <c r="W3" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X3" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y3" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -1732,18 +1939,26 @@
       </c>
       <c r="Z3" s="11" t="n"/>
       <c r="AA3" s="11" t="n"/>
-      <c r="AB3" s="11" t="n"/>
+      <c r="AB3" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Lavender extract; turmeric; honeysuckle; jojoba</t>
+        </is>
+      </c>
       <c r="AC3" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD3" s="15" t="n"/>
+      <c r="AD3" s="38" t="inlineStr">
+        <is>
+          <t>Full $176.50 / travel $88</t>
+        </is>
+      </c>
       <c r="AE3" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>1</v>
       </c>
@@ -1818,18 +2033,44 @@
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="11" t="n"/>
-      <c r="R4" s="11" t="n"/>
-      <c r="S4" s="11" t="n"/>
-      <c r="T4" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U4" s="11" t="n"/>
-      <c r="V4" s="11" t="n"/>
-      <c r="W4" s="11" t="n"/>
-      <c r="X4" s="11" t="n"/>
+      <c r="Q4" s="32" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="R4" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S4" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T4" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U4" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V4" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, Sodium Cocoyl Wheat Amino Acids, Coconut-Derived Betaine, Red Algae Extract, Brown Algae Extract, German Chamomile Oil, Ginger Root Oil, Guaran Extract, Glycerol, Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="W4" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X4" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y4" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -1837,18 +2078,26 @@
       </c>
       <c r="Z4" s="11" t="n"/>
       <c r="AA4" s="11" t="n"/>
-      <c r="AB4" s="11" t="n"/>
+      <c r="AB4" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: German Chamomile Oil; Ginger Root Oil</t>
+        </is>
+      </c>
       <c r="AC4" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD4" s="15" t="n"/>
+      <c r="AD4" s="38" t="inlineStr">
+        <is>
+          <t>Two essential oils present. Full $56.50 / travel $42</t>
+        </is>
+      </c>
       <c r="AE4" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>1</v>
       </c>
@@ -1923,18 +2172,44 @@
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="11" t="n"/>
-      <c r="R5" s="11" t="n"/>
-      <c r="S5" s="11" t="n"/>
-      <c r="T5" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U5" s="11" t="n"/>
-      <c r="V5" s="11" t="n"/>
-      <c r="W5" s="11" t="n"/>
-      <c r="X5" s="11" t="n"/>
+      <c r="Q5" s="32" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="R5" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S5" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T5" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U5" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V5" s="36" t="inlineStr">
+        <is>
+          <t>Water, Dimethicone, Cyclopentasiloxane, Glycerin, Nicotinamide Mononucleotide, Hyaluronic Acid, Panthenol, Glycosaminoglycans, Acetyl Glutamylheptapeptide-1, Copper Tripeptide-1, Copper PCA, Zinc PCA, Calcium PCA, Laureth-12, Squalene, Santalum Album (Sandalwood) Extract, Phellodendron Amurense Bark Extract, Hordeum Distichon (Barley) Extract, Aloe Barbadensis Leaf Extract, Hydrolyzed Wheat Protein, Phytic Acid, Triticum Vulgare (Wheat) Germ Oil, Linoleic Acid, Simmondsia Chinensis (Jojoba) Seed Oil, Propylene Glycol, Sorbitol, Tocopherol, Urtica Dioica (Nettle) Extract, Equisetum Arvense (Horsetail) Extract, Cucumis Sativus (Cucumber) Extract, Centella Asiatica Extract, Chamomilla Recutita Extract, Chlorella Vulgaris Extract, Hydrolyzed Algin, Lecithin, Phenoxyethanol, Caprylyl Glycol, Ethylhexylglycerin, Hexylene Glycol</t>
+        </is>
+      </c>
+      <c r="W5" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X5" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y5" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -1942,18 +2217,26 @@
       </c>
       <c r="Z5" s="11" t="n"/>
       <c r="AA5" s="11" t="n"/>
-      <c r="AB5" s="11" t="n"/>
+      <c r="AB5" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Sandalwood extract; chamomile</t>
+        </is>
+      </c>
       <c r="AC5" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD5" s="15" t="n"/>
+      <c r="AD5" s="38" t="inlineStr">
+        <is>
+          <t>Single size</t>
+        </is>
+      </c>
       <c r="AE5" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>1</v>
       </c>
@@ -2028,18 +2311,44 @@
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="11" t="n"/>
-      <c r="R6" s="11" t="n"/>
-      <c r="S6" s="11" t="n"/>
-      <c r="T6" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U6" s="11" t="n"/>
-      <c r="V6" s="11" t="n"/>
-      <c r="W6" s="11" t="n"/>
-      <c r="X6" s="11" t="n"/>
+      <c r="Q6" s="32" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="R6" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S6" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T6" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U6" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V6" s="36" t="inlineStr">
+        <is>
+          <t>ACTIVE: Non-Nano Zinc Oxide 17%. INACTIVE: Water, Caprylic/Capric Triglyceride, Isododecane, Propanediol, Polyglyceryl-6 Polyricinoleate, C12-15 Alkyl Benzoate, Dimethylmethoxy Chromanol, Dimethicone, Polymethylsilsesquioxane/Trimethylsiloxysilicate, Coco-Caprylate/Caprate, Betula Alba (Birch) Bark Extract, Ethylhexyl Palmitate, Polymethylsilsesquioxane, Disteardimonium Hectorite, Polyglyceryl-10 Dioleate, Polyhydroxystearic Acid, Lecithin, Jojoba Esters, Ectoin, Boswellia Serrata Extract, Polygonum Cuspidatum Root Extract, Centella Asiatica Extract, Butyrospermum Parkii (Shea) Butter, Glycerin, Lavandula Angustifolia (Lavender) Oil, Pelargonium Graveolens (Rose Geranium) Flower Oil, Tapioca Starch Polymethylsilsesquioxane, Propylene Carbonate, Polysilicone-11, Tromethamine, Polyglyceryl-10 Laurate, Octyldodecanol, Trihydroxystearin, Alumina, Silica, Ethylhexylglycerin, Titanium Dioxide (CI 77891), Iron Oxide (CI 77491, CI 77492), Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="W6" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X6" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y6" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -2047,15 +2356,19 @@
       </c>
       <c r="Z6" s="11" t="n"/>
       <c r="AA6" s="11" t="n"/>
-      <c r="AB6" s="11" t="n"/>
+      <c r="AB6" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Lavender Oil; Rose Geranium Flower Oil; Frankincense</t>
+        </is>
+      </c>
       <c r="AC6" s="14" t="inlineStr">
         <is>
           <t>blocked</t>
         </is>
       </c>
-      <c r="AD6" s="16" t="inlineStr">
-        <is>
-          <t>BLOCKER (Phase 9F): publishes an OTC-style ingredient list with NO Drug Facts panel, no warnings, no broad-spectrum statement. US sunscreens are OTC drugs. Cannot be approved until resolved with the brand.</t>
+      <c r="AD6" s="39" t="inlineStr">
+        <is>
+          <t>BLOCKER (Phase 9F): publishes an OTC-style ingredient list with NO Drug Facts panel, no warnings, no broad-spectrum statement. US sunscreens are OTC drugs. Cannot be approved until resolved with the brand. | CONFIRMED 2026-09-04: active % IS stated (zinc 17%) but NO Drug Facts panel, NO warnings, NO broad-spectrum statement in page body. Currently SOLD OUT and delisted from /collections/all-products</t>
         </is>
       </c>
       <c r="AE6" s="14" t="inlineStr">
@@ -2064,7 +2377,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="42" customHeight="1">
+    <row r="7" ht="58" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>1</v>
       </c>
@@ -2139,18 +2452,44 @@
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="11" t="n"/>
-      <c r="R7" s="11" t="n"/>
-      <c r="S7" s="11" t="n"/>
-      <c r="T7" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U7" s="11" t="n"/>
-      <c r="V7" s="11" t="n"/>
-      <c r="W7" s="11" t="n"/>
-      <c r="X7" s="11" t="n"/>
+      <c r="Q7" s="32" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="R7" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S7" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T7" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U7" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V7" s="36" t="inlineStr">
+        <is>
+          <t>Water, Glycerin, Tetrapeptide-4, Yeast Extract, Hydrolyzed Algin, Fragaria Ananassa (Strawberry) Seed Extract, Mannitol, Moringa Oleifera Seed Oil, Sea Water, Sucrose, Melia Azadirachta Extract, Rosa Damascena (Damask Rose) Flower Oil, Carbomer, Sorbitan Oleate Decylglucoside Crosspolymer, Caprylyl Glycol, Sodium Hydroxide, Hexylene Glycol, Tetrasodium Glutamate Diacetate, Propanediol, Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="W7" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X7" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y7" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -2158,18 +2497,26 @@
       </c>
       <c r="Z7" s="11" t="n"/>
       <c r="AA7" s="11" t="n"/>
-      <c r="AB7" s="11" t="n"/>
+      <c r="AB7" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Damask Rose Flower Oil</t>
+        </is>
+      </c>
       <c r="AC7" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD7" s="15" t="n"/>
+      <c r="AD7" s="38" t="inlineStr">
+        <is>
+          <t>Full $151.50 / travel $75</t>
+        </is>
+      </c>
       <c r="AE7" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="8" ht="42" customHeight="1">
+    <row r="8" ht="58" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>1</v>
       </c>
@@ -2244,18 +2591,44 @@
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="11" t="n"/>
-      <c r="R8" s="11" t="n"/>
-      <c r="S8" s="11" t="n"/>
-      <c r="T8" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U8" s="11" t="n"/>
-      <c r="V8" s="11" t="n"/>
-      <c r="W8" s="11" t="n"/>
-      <c r="X8" s="11" t="n"/>
+      <c r="Q8" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="R8" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S8" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T8" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U8" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V8" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin, Isoprene Glycol, Polysorbate 20, Dipentylene Glycol, Chamomilla Recutita Flower Extract, Copper Tripeptide, Cucumis Sativus Fruit Extract, Aloe Barbadensis Leaf Juice, Helianthus Annuus Sprout Extract, Maltodextrin, Nicotinamide Mononucleotide, Lecithin, Ectoin, Plankton Extract, Spirulina Platensis Extract, Menthyl Nicotinate, Coccinia Indica Fruit Extract, Eclipta Prostrata Extract, 1,2-Hexanediol, Caprylyl Glycol, Vanillyl Butyl Ether, Ergothioneine, Tricholoma Matsutake Mycelium Ferment Extract, Tricholoma Matsutake Extract, Superoxide Dismutase, Methylthioninium Chloride (Methylene Blue)</t>
+        </is>
+      </c>
+      <c r="W8" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X8" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y8" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -2263,18 +2636,26 @@
       </c>
       <c r="Z8" s="11" t="n"/>
       <c r="AA8" s="11" t="n"/>
-      <c r="AB8" s="11" t="n"/>
+      <c r="AB8" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Chamomile flower extract</t>
+        </is>
+      </c>
       <c r="AC8" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD8" s="15" t="n"/>
+      <c r="AD8" s="38" t="inlineStr">
+        <is>
+          <t>Contains Menthyl Nicotinate (menthol derivative). Full $65 / travel $35</t>
+        </is>
+      </c>
       <c r="AE8" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="42" customHeight="1">
+    <row r="9" ht="58" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>1</v>
       </c>
@@ -2349,18 +2730,44 @@
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="11" t="n"/>
-      <c r="R9" s="11" t="n"/>
-      <c r="S9" s="11" t="n"/>
-      <c r="T9" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U9" s="11" t="n"/>
-      <c r="V9" s="11" t="n"/>
-      <c r="W9" s="11" t="n"/>
-      <c r="X9" s="11" t="n"/>
+      <c r="Q9" s="32" t="n">
+        <v>285</v>
+      </c>
+      <c r="R9" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S9" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T9" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U9" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V9" s="36" t="inlineStr">
+        <is>
+          <t>Water, Carbomer, Hydroxyethylcellulose, Carbopol, Isoprene Glycol, Glycerine, Human Platelet Extract, Sodium Chloride, Hyaluronic Acid, Beta-Glucan, Panthenol, Polyacrylate Crosspolymer-6, Phenyl Trimethicone, Helianthus Annuus Sprout Extract, Maltodextrin, Bifida Ferment Filtrate, Pentylene Glycol, 1,2-Hexanediol, Caprylyl Glycol</t>
+        </is>
+      </c>
+      <c r="W9" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X9" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y9" s="17" t="inlineStr">
         <is>
           <t>PRACTITIONER ONLY (provisional)</t>
@@ -2374,9 +2781,9 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="AD9" s="16" t="inlineStr">
-        <is>
-          <t>BLOCKER (Phase 9F): contains human platelet extract in a topical cosmetic. Practitioner and jurisdiction review required before any consumer recommendation.</t>
+      <c r="AD9" s="39" t="inlineStr">
+        <is>
+          <t>BLOCKER (Phase 9F): contains human platelet extract in a topical cosmetic. Practitioner and jurisdiction review required before any consumer recommendation. | Human platelet extract confirmed in published INCI. Practitioner/jurisdiction review required</t>
         </is>
       </c>
       <c r="AE9" s="14" t="inlineStr">
@@ -2385,7 +2792,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="42" customHeight="1">
+    <row r="10" ht="58" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>1</v>
       </c>
@@ -2460,18 +2867,44 @@
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="11" t="n"/>
-      <c r="R10" s="11" t="n"/>
-      <c r="S10" s="11" t="n"/>
-      <c r="T10" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U10" s="11" t="n"/>
-      <c r="V10" s="11" t="n"/>
-      <c r="W10" s="11" t="n"/>
-      <c r="X10" s="11" t="n"/>
+      <c r="Q10" s="32" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="R10" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S10" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T10" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U10" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V10" s="36" t="inlineStr">
+        <is>
+          <t>Dimethiconol, Ethylhexyl Cocoate, Glycine Soja (Soybean) Oil, Retinol, Phospholipids, Glycolipids, Cyclopentasiloxane, Glycine Soja (Soybean) Lecithin, Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="W10" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X10" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y10" s="17" t="inlineStr">
         <is>
           <t>AVOID (provisional)</t>
@@ -2485,12 +2918,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD10" s="15" t="n"/>
+      <c r="AD10" s="38" t="inlineStr">
+        <is>
+          <t>Retinol % NOT stated. Delisted from /collections/all-products; reachable via sitemap only</t>
+        </is>
+      </c>
       <c r="AE10" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="11" ht="42" customHeight="1">
+    <row r="11" ht="58" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>1</v>
       </c>
@@ -2565,18 +3002,44 @@
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="11" t="n"/>
-      <c r="R11" s="11" t="n"/>
-      <c r="S11" s="11" t="n"/>
-      <c r="T11" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U11" s="11" t="n"/>
-      <c r="V11" s="11" t="n"/>
-      <c r="W11" s="11" t="n"/>
-      <c r="X11" s="11" t="n"/>
+      <c r="Q11" s="32" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="R11" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S11" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T11" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U11" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V11" s="36" t="inlineStr">
+        <is>
+          <t>Water, Glycerin, Isoprene Glycol, Resveratrol, Spirulina Platensis Extract, Spermidine (CelVio), Nicotinamide Mononucleotide, Hydroxyethylcellulose, Palmitoyl Hexapeptide-12, Tetrahexyldecyl Ascorbate, Hyaluronic Acid, Squalane, Panthenol, Helianthus Annuus Sprout Extract, Maltodextrin, Camellia Sinensis (White Tea) Leaf Extract, Undecane, Tridecane, Pentaerythrityl Tetraisostearate, Caprylic/Capric Triglyceride, Stearalkonium Hectorite, Propylene Carbonate, Carbomer, Butylene Glycol, Plankton Extract, Ergothioneine, Tricholoma Matsutake Mycelium Ferment Extract, Tricholoma Matsutake Extract, Ectoin, Lavandula Angustifolia (French Lavender) Extract, Lonicera Caprifolium Flower Extract, Lonicera Japonica Flower Extract, Simmondsia Chinensis (Jojoba) Seed Oil, Citric Acid, Melia Azadirachta Leaf Extract, Melia Azadirachta Flower Extract, Corallina Officinalis Extract</t>
+        </is>
+      </c>
+      <c r="W11" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X11" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y11" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -2584,18 +3047,26 @@
       </c>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="11" t="n"/>
-      <c r="AB11" s="11" t="n"/>
+      <c r="AB11" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Lavender extract; white tea; honeysuckle; neem flower</t>
+        </is>
+      </c>
       <c r="AC11" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD11" s="15" t="n"/>
+      <c r="AD11" s="38" t="inlineStr">
+        <is>
+          <t>Listed on site as L.A.D.R. SERUM</t>
+        </is>
+      </c>
       <c r="AE11" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="12" ht="42" customHeight="1">
+    <row r="12" ht="58" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>1</v>
       </c>
@@ -2670,18 +3141,44 @@
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="11" t="n"/>
-      <c r="R12" s="11" t="n"/>
-      <c r="S12" s="11" t="n"/>
-      <c r="T12" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U12" s="11" t="n"/>
-      <c r="V12" s="11" t="n"/>
-      <c r="W12" s="11" t="n"/>
-      <c r="X12" s="11" t="n"/>
+      <c r="Q12" s="32" t="n">
+        <v>200</v>
+      </c>
+      <c r="R12" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S12" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T12" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U12" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V12" s="36" t="inlineStr">
+        <is>
+          <t>Water, Caprylic/Capric Triglyceride, Glycerine, Nicotinamide Mononucleotide, Resveratrol, CelVio Spermidine, Palmitoyl Hexapeptide-12, Phenyl Trimethicone, Tetrahexyldecyl Ascorbate, Squalane, Isoprene Glycol, Xylitylglucoside, Anhydroxylitol, Xylitol, Maltodextrin, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Shorea Robusta Seed Butter, Cera Alba (Beeswax), Polyglyceryl-3 Distearate, Cetearyl Glucoside, Cetyl Alcohol, Heptyl Undecylenate, Hydroxyethylcellulose, Lonicera Caprifolium Flower Extract, Lonicera Japonica Flower Extract, Simmondsia Chinensis (Jojoba) Seed Oil, Pentaerythrityl Tetraisostearate, Stearalkonium Hectorite, Propylene Carbonate, Disodium EDTA, Pelargonium Graveolens (Geranium) Oil, Citric Acid</t>
+        </is>
+      </c>
+      <c r="W12" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X12" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y12" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -2689,18 +3186,26 @@
       </c>
       <c r="Z12" s="11" t="n"/>
       <c r="AA12" s="11" t="n"/>
-      <c r="AB12" s="11" t="n"/>
+      <c r="AB12" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Geranium Oil; honeysuckle</t>
+        </is>
+      </c>
       <c r="AC12" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD12" s="15" t="n"/>
+      <c r="AD12" s="38" t="inlineStr">
+        <is>
+          <t>Full $200 / travel $120</t>
+        </is>
+      </c>
       <c r="AE12" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="13" ht="42" customHeight="1">
+    <row r="13" ht="58" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>1</v>
       </c>
@@ -2775,18 +3280,44 @@
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="11" t="n"/>
-      <c r="R13" s="11" t="n"/>
-      <c r="S13" s="11" t="n"/>
-      <c r="T13" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U13" s="11" t="n"/>
-      <c r="V13" s="11" t="n"/>
-      <c r="W13" s="11" t="n"/>
-      <c r="X13" s="11" t="n"/>
+      <c r="Q13" s="32" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="R13" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S13" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T13" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U13" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V13" s="36" t="inlineStr">
+        <is>
+          <t>Hydrogenated Polyisobutene, Isononyl Isononanoate, Ethylene/Propylene/Styrene Copolymer, Butylene/Ethylene/Styrene Copolymer, Flavor, Benzyl Nicotinate, Dimethylmethoxy Chromanyl Palmitate, Dimethylmethoxy Chromanol, Palmitoyl Tripeptide-38, Limnanthes Alba (Meadowfoam) Seed Oil, Ricinus Communis (Castor) Seed Oil, Portulaca Pilosa Extract, Sucrose Cocoate, Cetearyl Ethylhexanoate, Glycerin, Phenoxyethanol, Neopentyl Glycol Dicaprylate/Dicaprate, Tridecyl Stearate, Sucralose, Sorbitan Isostearate, Tridecyl Trimellitate, Titanium Dioxide (CI 77891)</t>
+        </is>
+      </c>
+      <c r="W13" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X13" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y13" s="17" t="inlineStr">
         <is>
           <t>CAUTION (provisional)</t>
@@ -2794,18 +3325,26 @@
       </c>
       <c r="Z13" s="11" t="n"/>
       <c r="AA13" s="11" t="n"/>
-      <c r="AB13" s="11" t="n"/>
+      <c r="AB13" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: undisclosed Flavor</t>
+        </is>
+      </c>
       <c r="AC13" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD13" s="15" t="n"/>
+      <c r="AD13" s="38" t="inlineStr">
+        <is>
+          <t>Contains undisclosed 'Flavor' + Sucralose. Lip product</t>
+        </is>
+      </c>
       <c r="AE13" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="14" ht="42" customHeight="1">
+    <row r="14" ht="58" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>1</v>
       </c>
@@ -2881,15 +3420,27 @@
       </c>
       <c r="P14" s="3" t="inlineStr"/>
       <c r="Q14" s="11" t="n"/>
-      <c r="R14" s="11" t="n"/>
+      <c r="R14" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
       <c r="S14" s="11" t="n"/>
-      <c r="T14" s="12" t="inlineStr">
+      <c r="T14" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U14" s="11" t="n"/>
-      <c r="V14" s="11" t="n"/>
+      <c r="U14" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="V14" s="43" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
       <c r="W14" s="11" t="n"/>
       <c r="X14" s="11" t="n"/>
       <c r="Y14" s="13" t="inlineStr">
@@ -2905,12 +3456,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD14" s="15" t="n"/>
+      <c r="AD14" s="38" t="inlineStr">
+        <is>
+          <t>NOT FOUND: absent from the 54-URL product sitemap and on-site search. Likely discontinued — re-identify or drop</t>
+        </is>
+      </c>
       <c r="AE14" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="15" ht="42" customHeight="1">
+    <row r="15" ht="58" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>1</v>
       </c>
@@ -2985,18 +3540,44 @@
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="11" t="n"/>
-      <c r="R15" s="11" t="n"/>
-      <c r="S15" s="11" t="n"/>
-      <c r="T15" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U15" s="11" t="n"/>
-      <c r="V15" s="11" t="n"/>
-      <c r="W15" s="11" t="n"/>
-      <c r="X15" s="11" t="n"/>
+      <c r="Q15" s="32" t="n">
+        <v>125</v>
+      </c>
+      <c r="R15" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S15" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T15" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U15" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V15" s="36" t="inlineStr">
+        <is>
+          <t>Water, Caprylic/Capric Triglyceride, Glycerin, Phenyl Trimethicone, Nicotinamide Mononucleotide, Caprooyl Tetrapeptide-3, Palmitoyl Hexapeptide-12, Spermidine, Isoprene Glycol, Ergothioneine, Helianthus Annuus Sprout Extract, Maltodextrin, Tricholoma Matsutake Mycelium Ferment Extract, Tricholoma Matsutake Extract, Shorea Robusta Seed Butter, Hydroxyethyl Acrylate/Sodium Acryloyldimethyl Taurate Copolymer, Polyglyceryl-3 Distearate, Rosa Damascena Flower Wax, Heptyl Undecylenate, Isoamyl Laurate, Pentaerythrityl Tetraisostearate, Stearalkonium Hectorite, Propylene Carbonate, Cetyl Alcohol, Dextran, Hydroxyethylcellulose, Lonicera Caprifolium Flower Extract, Lonicera Japonica Flower Extract, Simmondsia Chinensis (Jojoba) Seed Oil, Trisodium EDTA, Cymbopogon Flexuosus (Lemongrass) Leaf Oil, Citric Acid</t>
+        </is>
+      </c>
+      <c r="W15" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X15" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y15" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -3004,18 +3585,26 @@
       </c>
       <c r="Z15" s="11" t="n"/>
       <c r="AA15" s="11" t="n"/>
-      <c r="AB15" s="11" t="n"/>
+      <c r="AB15" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Lemongrass Leaf Oil; Damask Rose Flower Wax; honeysuckle</t>
+        </is>
+      </c>
       <c r="AC15" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD15" s="15" t="n"/>
+      <c r="AD15" s="38" t="inlineStr">
+        <is>
+          <t>Regular $125, on 20% sale at capture</t>
+        </is>
+      </c>
       <c r="AE15" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="16" ht="42" customHeight="1">
+    <row r="16" ht="58" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>1</v>
       </c>
@@ -3090,18 +3679,44 @@
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="11" t="n"/>
-      <c r="R16" s="11" t="n"/>
-      <c r="S16" s="11" t="n"/>
-      <c r="T16" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U16" s="11" t="n"/>
-      <c r="V16" s="11" t="n"/>
-      <c r="W16" s="11" t="n"/>
-      <c r="X16" s="11" t="n"/>
+      <c r="Q16" s="32" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="R16" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S16" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T16" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U16" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V16" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, Nicotinamide, Ectoin, Glycerol, Saccharomyces Cerevisiae Extract, Simmondsia Chinensis Seed Oil Nano-Particles, Squalane, Phospholipids, Sodium Hyaluronate, Caprylic/Capric Triglyceride, Sodium Polyacryloyldimethyl Taurate, Propanediol, Tetrasodium Glutamate Diacetate, Citric Acid, Xanthan Gum, Ethylhexylglycerin, Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="W16" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X16" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y16" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -3115,12 +3730,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD16" s="15" t="n"/>
+      <c r="AD16" s="38" t="inlineStr">
+        <is>
+          <t>Published INCI contains non-INCI code string 'A845925 Nicotinamide'</t>
+        </is>
+      </c>
       <c r="AE16" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="17" ht="42" customHeight="1">
+    <row r="17" ht="58" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>1</v>
       </c>
@@ -3195,18 +3814,44 @@
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="11" t="n"/>
-      <c r="R17" s="11" t="n"/>
-      <c r="S17" s="11" t="n"/>
-      <c r="T17" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U17" s="11" t="n"/>
-      <c r="V17" s="11" t="n"/>
-      <c r="W17" s="11" t="n"/>
-      <c r="X17" s="11" t="n"/>
+      <c r="Q17" s="32" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="R17" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S17" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T17" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U17" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V17" s="36" t="inlineStr">
+        <is>
+          <t>Cyclopentasiloxane, Dimethylmethoxy Chromanol, Octyl Cocoate, Glycolipids, Dimethiconol, Glyceryl Linoleate, Glyceryl Linolenate, Alpha Tocopheryl Acetate, Lecithin, Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="W17" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X17" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y17" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -3220,12 +3865,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD17" s="15" t="n"/>
+      <c r="AD17" s="38" t="inlineStr">
+        <is>
+          <t>Delisted from /collections/all-products; sitemap only</t>
+        </is>
+      </c>
       <c r="AE17" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="18" ht="42" customHeight="1">
+    <row r="18" ht="58" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>1</v>
       </c>
@@ -3300,18 +3949,44 @@
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="11" t="n"/>
-      <c r="R18" s="11" t="n"/>
-      <c r="S18" s="11" t="n"/>
-      <c r="T18" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U18" s="11" t="n"/>
-      <c r="V18" s="11" t="n"/>
-      <c r="W18" s="11" t="n"/>
-      <c r="X18" s="11" t="n"/>
+      <c r="Q18" s="32" t="n">
+        <v>151.5</v>
+      </c>
+      <c r="R18" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S18" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T18" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U18" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V18" s="36" t="inlineStr">
+        <is>
+          <t>Water, Polyhydroxybutyrate, Lactobacillus/Punica Granatum Fruit Ferment Extract, Sucrose Cocoate, Carthamus Tinctorius (Safflower) Seed Oil, Glycerin, Niacinamide, Panthenol, Cetyl Alcohol, Stearic Acid, Cocos Nucifera (Coconut) Oil, Sodium Lauroyl Sarcosinate, Glyceryl Stearate SE, Carrageenan, Carbomer, Sorbitan Stearate, Sodium Hydroxide, Ethylhexylglycerin, Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="W18" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X18" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y18" s="17" t="inlineStr">
         <is>
           <t>CAUTION (provisional)</t>
@@ -3325,12 +4000,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD18" s="15" t="n"/>
+      <c r="AD18" s="38" t="inlineStr">
+        <is>
+          <t>URL slug is 'probiotic-polish'; delisted from /collections/all-products</t>
+        </is>
+      </c>
       <c r="AE18" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="19" ht="42" customHeight="1">
+    <row r="19" ht="58" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>1</v>
       </c>
@@ -3405,18 +4084,44 @@
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="11" t="n"/>
-      <c r="R19" s="11" t="n"/>
-      <c r="S19" s="11" t="n"/>
-      <c r="T19" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U19" s="11" t="n"/>
-      <c r="V19" s="11" t="n"/>
-      <c r="W19" s="11" t="n"/>
-      <c r="X19" s="11" t="n"/>
+      <c r="Q19" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="R19" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S19" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T19" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U19" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V19" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin, Isoprene Glycol, Polysorbate 20, Dipentylene Glycol, Chamomilla Recutita Flower Extract, Copper Tripeptide, Cucumis Sativus Fruit Extract, Aloe Barbadensis Leaf Juice, Helianthus Annuus Sprout Extract, Maltodextrin, Nicotinamide Mononucleotide, Lecithin, Ectoin, Plankton Extract, Spirulina Platensis Extract, Menthyl Nicotinate, Coccinia Indica Fruit Extract, Eclipta Prostrata Extract, 1,2-Hexanediol, Caprylyl Glycol, Vanillyl Butyl Ether, Ergothioneine, Tricholoma Matsutake Mycelium Ferment Extract, Tricholoma Matsutake Extract, Superoxide Dismutase, Methylthioninium Chloride (Methylene Blue)</t>
+        </is>
+      </c>
+      <c r="W19" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="X19" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y19" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -3424,18 +4129,26 @@
       </c>
       <c r="Z19" s="11" t="n"/>
       <c r="AA19" s="11" t="n"/>
-      <c r="AB19" s="11" t="n"/>
+      <c r="AB19" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Chamomile flower extract</t>
+        </is>
+      </c>
       <c r="AC19" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD19" s="15" t="n"/>
+      <c r="AD19" s="38" t="inlineStr">
+        <is>
+          <t>Travel variant of BLUE PEPTIDE SPRAY, not a separate page. 15 mL volume NOT printed on page</t>
+        </is>
+      </c>
       <c r="AE19" s="14" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="20" ht="42" customHeight="1">
+    <row r="20" ht="58" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>1</v>
       </c>
@@ -3511,15 +4224,27 @@
       </c>
       <c r="P20" s="3" t="inlineStr"/>
       <c r="Q20" s="11" t="n"/>
-      <c r="R20" s="11" t="n"/>
+      <c r="R20" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
       <c r="S20" s="11" t="n"/>
-      <c r="T20" s="12" t="inlineStr">
+      <c r="T20" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U20" s="11" t="n"/>
-      <c r="V20" s="11" t="n"/>
+      <c r="U20" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="V20" s="43" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
       <c r="W20" s="11" t="n"/>
       <c r="X20" s="11" t="n"/>
       <c r="Y20" s="13" t="inlineStr">
@@ -3535,12 +4260,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD20" s="15" t="n"/>
+      <c r="AD20" s="38" t="inlineStr">
+        <is>
+          <t>NOT FOUND: parent product absent from sitemap. Likely discontinued</t>
+        </is>
+      </c>
       <c r="AE20" s="14" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="21" ht="42" customHeight="1">
+    <row r="21" ht="58" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>1</v>
       </c>
@@ -3615,16 +4344,34 @@
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="11" t="n"/>
-      <c r="R21" s="11" t="n"/>
-      <c r="S21" s="11" t="n"/>
-      <c r="T21" s="12" t="inlineStr">
+      <c r="Q21" s="32" t="n">
+        <v>477.5</v>
+      </c>
+      <c r="R21" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S21" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T21" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U21" s="11" t="n"/>
-      <c r="V21" s="11" t="n"/>
+      <c r="U21" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V21" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W21" s="11" t="n"/>
       <c r="X21" s="11" t="n"/>
       <c r="Y21" s="13" t="inlineStr">
@@ -3640,12 +4387,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD21" s="15" t="n"/>
+      <c r="AD21" s="38" t="inlineStr">
+        <is>
+          <t>Bundle — no single INCI</t>
+        </is>
+      </c>
       <c r="AE21" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
+    <row r="22" ht="58" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>1</v>
       </c>
@@ -3720,16 +4471,34 @@
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="11" t="n"/>
-      <c r="R22" s="11" t="n"/>
-      <c r="S22" s="11" t="n"/>
-      <c r="T22" s="12" t="inlineStr">
+      <c r="Q22" s="32" t="n">
+        <v>354.35</v>
+      </c>
+      <c r="R22" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S22" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T22" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U22" s="11" t="n"/>
-      <c r="V22" s="11" t="n"/>
+      <c r="U22" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V22" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W22" s="11" t="n"/>
       <c r="X22" s="11" t="n"/>
       <c r="Y22" s="13" t="inlineStr">
@@ -3745,12 +4514,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD22" s="15" t="n"/>
+      <c r="AD22" s="38" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
       <c r="AE22" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="58" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>1</v>
       </c>
@@ -3825,16 +4598,34 @@
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="11" t="n"/>
-      <c r="R23" s="11" t="n"/>
-      <c r="S23" s="11" t="n"/>
-      <c r="T23" s="12" t="inlineStr">
+      <c r="Q23" s="32" t="n">
+        <v>757.5</v>
+      </c>
+      <c r="R23" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S23" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T23" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U23" s="11" t="n"/>
-      <c r="V23" s="11" t="n"/>
+      <c r="U23" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V23" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W23" s="11" t="n"/>
       <c r="X23" s="11" t="n"/>
       <c r="Y23" s="13" t="inlineStr">
@@ -3850,12 +4641,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD23" s="15" t="n"/>
+      <c r="AD23" s="38" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
       <c r="AE23" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
+    <row r="24" ht="58" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>1</v>
       </c>
@@ -3930,16 +4725,34 @@
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="11" t="n"/>
-      <c r="R24" s="11" t="n"/>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="12" t="inlineStr">
+      <c r="Q24" s="32" t="n">
+        <v>1335</v>
+      </c>
+      <c r="R24" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S24" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T24" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U24" s="11" t="n"/>
-      <c r="V24" s="11" t="n"/>
+      <c r="U24" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V24" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W24" s="11" t="n"/>
       <c r="X24" s="11" t="n"/>
       <c r="Y24" s="13" t="inlineStr">
@@ -3955,12 +4768,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD24" s="15" t="n"/>
+      <c r="AD24" s="38" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
       <c r="AE24" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
+    <row r="25" ht="58" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>1</v>
       </c>
@@ -4035,16 +4852,34 @@
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="11" t="n"/>
-      <c r="R25" s="11" t="n"/>
-      <c r="S25" s="11" t="n"/>
-      <c r="T25" s="12" t="inlineStr">
+      <c r="Q25" s="32" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="R25" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S25" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T25" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U25" s="11" t="n"/>
-      <c r="V25" s="11" t="n"/>
+      <c r="U25" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V25" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W25" s="11" t="n"/>
       <c r="X25" s="11" t="n"/>
       <c r="Y25" s="13" t="inlineStr">
@@ -4060,12 +4895,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD25" s="15" t="n"/>
+      <c r="AD25" s="38" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
       <c r="AE25" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="26" ht="42" customHeight="1">
+    <row r="26" ht="58" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>1</v>
       </c>
@@ -4140,16 +4979,34 @@
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="11" t="n"/>
-      <c r="R26" s="11" t="n"/>
-      <c r="S26" s="11" t="n"/>
-      <c r="T26" s="12" t="inlineStr">
+      <c r="Q26" s="32" t="n">
+        <v>563.33</v>
+      </c>
+      <c r="R26" s="33" t="inlineStr">
+        <is>
+          <t>https://www.younggoose.com</t>
+        </is>
+      </c>
+      <c r="S26" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T26" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U26" s="11" t="n"/>
-      <c r="V26" s="11" t="n"/>
+      <c r="U26" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V26" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W26" s="11" t="n"/>
       <c r="X26" s="11" t="n"/>
       <c r="Y26" s="13" t="inlineStr">
@@ -4165,12 +5022,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD26" s="15" t="n"/>
+      <c r="AD26" s="38" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
       <c r="AE26" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="27" ht="42" customHeight="1">
+    <row r="27" ht="58" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>1</v>
       </c>
@@ -4245,18 +5106,44 @@
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="11" t="n"/>
-      <c r="R27" s="11" t="n"/>
-      <c r="S27" s="11" t="n"/>
-      <c r="T27" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U27" s="11" t="n"/>
-      <c r="V27" s="11" t="n"/>
-      <c r="W27" s="11" t="n"/>
-      <c r="X27" s="11" t="n"/>
+      <c r="Q27" s="32" t="n">
+        <v>119</v>
+      </c>
+      <c r="R27" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S27" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T27" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U27" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V27" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, GHK-Cu, Palmitoyl Tripeptide-1, Macrocystis Pyrifera (Brown Algae Extract), Xanthan Gum, Sodium PCA, Allantoin, Silk Amino Acids, Hyaluronic Acid, Phenoxyethanol, Caprylyl Glycol, Sorbic Acid</t>
+        </is>
+      </c>
+      <c r="W27" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X27" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y27" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -4270,12 +5157,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD27" s="15" t="n"/>
+      <c r="AD27" s="38" t="inlineStr">
+        <is>
+          <t>2% confirmed on page. INCI from site-wide /pages/total-ingredients-list; the 2% and 3% share ONE undifferentiated list. Page states 'free from fragrances'</t>
+        </is>
+      </c>
       <c r="AE27" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="28" ht="42" customHeight="1">
+    <row r="28" ht="58" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>1</v>
       </c>
@@ -4350,18 +5241,44 @@
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="11" t="n"/>
-      <c r="R28" s="11" t="n"/>
-      <c r="S28" s="11" t="n"/>
-      <c r="T28" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U28" s="11" t="n"/>
-      <c r="V28" s="11" t="n"/>
-      <c r="W28" s="11" t="n"/>
-      <c r="X28" s="11" t="n"/>
+      <c r="Q28" s="32" t="n">
+        <v>189</v>
+      </c>
+      <c r="R28" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S28" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T28" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U28" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V28" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, GHK-Cu, Palmitoyl Tripeptide-1, Macrocystis Pyrifera (Brown Algae Extract), Xanthan Gum, Sodium PCA, Allantoin, Silk Amino Acids, Hyaluronic Acid, Phenoxyethanol, Caprylyl Glycol, Sorbic Acid</t>
+        </is>
+      </c>
+      <c r="W28" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X28" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y28" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -4375,12 +5292,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD28" s="15" t="n"/>
+      <c r="AD28" s="38" t="inlineStr">
+        <is>
+          <t>3% confirmed on page. SHARED INCI with the 2% — no 3%-specific list published</t>
+        </is>
+      </c>
       <c r="AE28" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="29" ht="42" customHeight="1">
+    <row r="29" ht="58" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>1</v>
       </c>
@@ -4455,18 +5376,44 @@
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr"/>
-      <c r="Q29" s="11" t="n"/>
-      <c r="R29" s="11" t="n"/>
-      <c r="S29" s="11" t="n"/>
-      <c r="T29" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U29" s="11" t="n"/>
-      <c r="V29" s="11" t="n"/>
-      <c r="W29" s="11" t="n"/>
-      <c r="X29" s="11" t="n"/>
+      <c r="Q29" s="32" t="n">
+        <v>99</v>
+      </c>
+      <c r="R29" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S29" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T29" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U29" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V29" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, Hyaluronic Acid, Xanthan Gum, Polyglyceryl-2 Dipolyhydroxystearate, Persea Gratissima (Avocado) Oil, Limnanthes Alba (Meadowfoam Seed) Oil, Cetyl Palmitate, Hippophae Rhamnoides (Sea Buckthorn) Oil, GHK-Cu, Glycerine, Stearic Acid, Hypericum Perforatum, Simmondsia Chinensis (Jojoba Seed) Oil, Panthenol, Calendula Officinalis Oil, D-Alpha-Tocopherol, Herbal Extract, Seaweed Extract, Butyrospermum Parkii (Shea) Butter, Coenzyme Q10, Alpha-Lipoic Acid, Superoxide Dismutase, Resveratrol, Coffea Arabica Oil, Squalane, Niacinamide, Phenoxyethanol, Ethylhexylglycerin</t>
+        </is>
+      </c>
+      <c r="W29" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X29" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y29" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -4474,18 +5421,26 @@
       </c>
       <c r="Z29" s="11" t="n"/>
       <c r="AA29" s="11" t="n"/>
-      <c r="AB29" s="11" t="n"/>
+      <c r="AB29" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Coffee Arabica Oil; Calendula Oil; St John's Wort; Sea Buckthorn Oil</t>
+        </is>
+      </c>
       <c r="AC29" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD29" s="15" t="n"/>
+      <c r="AD29" s="38" t="inlineStr">
+        <is>
+          <t>'Herbal Extract' and 'Seaweed Extract' undisclosed — allergen status of those cannot be determined</t>
+        </is>
+      </c>
       <c r="AE29" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="30" ht="42" customHeight="1">
+    <row r="30" ht="58" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>1</v>
       </c>
@@ -4560,18 +5515,44 @@
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="11" t="n"/>
-      <c r="R30" s="11" t="n"/>
-      <c r="S30" s="11" t="n"/>
-      <c r="T30" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U30" s="11" t="n"/>
-      <c r="V30" s="11" t="n"/>
-      <c r="W30" s="11" t="n"/>
-      <c r="X30" s="11" t="n"/>
+      <c r="Q30" s="32" t="n">
+        <v>89</v>
+      </c>
+      <c r="R30" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S30" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T30" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U30" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V30" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, GHK-Cu, Glyceryl Stearate, Polyglyceryl-6 Palmitate/Succinate, Cetearyl Alcohol, Isononyl Isononanoate, Ethylhexyl Olivate, Hesperidin Methyl Chalcone, Steareth-20, Dipeptide-2, Palmitoyl Tetrapeptide-7, Butyrospermum Parkii (Shea) Butter, Prunus Amygdalus Dulcis (Sweet Almond) Oil, Palmitoyl Tetrapeptide-1, Sodium Hyaluronate, Caprylhydroxamic Acid, Caprylyl Glycol, Glycerin, Xanthan Gum, Sodium Stearoyl Glutamate, Disodium EDTA</t>
+        </is>
+      </c>
+      <c r="W30" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X30" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y30" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -4585,12 +5566,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD30" s="15" t="n"/>
+      <c r="AD30" s="38" t="inlineStr">
+        <is>
+          <t>A separate mini travel size exists at $29</t>
+        </is>
+      </c>
       <c r="AE30" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="31" ht="42" customHeight="1">
+    <row r="31" ht="58" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>1</v>
       </c>
@@ -4665,18 +5650,44 @@
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="11" t="n"/>
-      <c r="R31" s="11" t="n"/>
-      <c r="S31" s="11" t="n"/>
-      <c r="T31" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U31" s="11" t="n"/>
-      <c r="V31" s="11" t="n"/>
-      <c r="W31" s="11" t="n"/>
-      <c r="X31" s="11" t="n"/>
+      <c r="Q31" s="32" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="R31" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S31" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T31" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U31" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V31" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, Organic blend of Calendula Officinalis, Arctium Lappa (Burdock Root), Salvia Officinalis (Sage), Urtica Dioica (Nettle), Rosmarinus Officinalis (Rosemary), Taraxacum Officinale (Dandelion), Equisetum Arvense (Horsetail), Angelica Archangelica, Hydrastis Canadensis (Goldenseal), Aloe Barbadensis, GHK-Cu, Polyglyceryl-2 Dipolyhydroxystearate, Seaweed Extract, Xanthan Gum, Butyrospermum Parkii (Shea Butter), Cocos Nucifera Oil, Tocopherol, Theobroma Cacao (Cocoa Seed Butter), Hypericum Perforatum (St John's Wort Oil), Vitamin E, Vegetable Glycerin, Panthenol, Hippophae Rhamnoides (Seabuckthorn Oil), Phenoxyethanol, Ethylhexylglycerin</t>
+        </is>
+      </c>
+      <c r="W31" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X31" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y31" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -4684,18 +5695,26 @@
       </c>
       <c r="Z31" s="11" t="n"/>
       <c r="AA31" s="11" t="n"/>
-      <c r="AB31" s="11" t="n"/>
+      <c r="AB31" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Rosemary; Sage; Angelica; Calendula; St John's Wort; Coconut; Cocoa Butter; Seabuckthorn</t>
+        </is>
+      </c>
       <c r="AC31" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD31" s="15" t="n"/>
+      <c r="AD31" s="38" t="inlineStr">
+        <is>
+          <t>Highest fragrant-botanical load in the Vitali line; herbal blend not broken to constituent level</t>
+        </is>
+      </c>
       <c r="AE31" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="32" ht="42" customHeight="1">
+    <row r="32" ht="58" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>1</v>
       </c>
@@ -4770,18 +5789,44 @@
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="11" t="n"/>
-      <c r="R32" s="11" t="n"/>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U32" s="11" t="n"/>
-      <c r="V32" s="11" t="n"/>
-      <c r="W32" s="11" t="n"/>
-      <c r="X32" s="11" t="n"/>
+      <c r="Q32" s="32" t="n">
+        <v>399</v>
+      </c>
+      <c r="R32" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S32" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T32" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U32" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V32" s="36" t="inlineStr">
+        <is>
+          <t>Water, Human Umbilical Mesenchymal Stem Cell Conditioned Media Filtrate, Palmitoyl Tripeptide-5, Pentylene Glycol, Polyacrylate Crosspolymer-11, Acetyl sh-Heptapeptide-1, Hydrolyzed Minnow Muscle Cell Lysate, Copper Tripeptide-1, Hydrogenated Lecithin, Ceramide NP, Ceramide AP, Ceramide EOP, Phytosphingosine, Cholesterol, Magnesium Ascorbyl Phosphate, Tetrahexyldecyl Ascorbate, Niacinamide, Sodium Hyaluronate, Glutathione, Pro Vitamin B-5, Glycerin, Butyrospermum Parkii (Shea) Butter, Glycyrrhiza Glabra Root Extract, Aloe Barbadensis Leaf Juice, Propylene Glycol, Urtica Dioica Extract, Faex Extract, Yeast Extract, Leuconostoc/Radish Root Ferment Filtrate, Lactobacillus, Cocos Nucifera Fruit Extract, Camellia Sinensis Leaf Extract, Avena Sativa Kernel Extract, Sodium Lauroyl Lactylate, Carbomer, Xanthan Gum, Arginine, Potassium Sorbate, Phenoxyethanol, Sodium Benzoate, Citric Acid, Phenethyl Alcohol, Ethylhexylglycerin</t>
+        </is>
+      </c>
+      <c r="W32" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X32" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y32" s="17" t="inlineStr">
         <is>
           <t>PRACTITIONER ONLY (provisional)</t>
@@ -4789,18 +5834,26 @@
       </c>
       <c r="Z32" s="11" t="n"/>
       <c r="AA32" s="11" t="n"/>
-      <c r="AB32" s="11" t="n"/>
+      <c r="AB32" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Phenethyl Alcohol (aromatic solvent, not on EU-26 list)</t>
+        </is>
+      </c>
       <c r="AC32" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD32" s="15" t="n"/>
+      <c r="AD32" s="38" t="inlineStr">
+        <is>
+          <t>Human umbilical stem cell conditioned media — same practitioner/jurisdiction question as Young Goose VAMPIRE EXOSOMES</t>
+        </is>
+      </c>
       <c r="AE32" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="33" ht="42" customHeight="1">
+    <row r="33" ht="58" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>1</v>
       </c>
@@ -4875,18 +5928,44 @@
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="11" t="n"/>
-      <c r="R33" s="11" t="n"/>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U33" s="11" t="n"/>
-      <c r="V33" s="11" t="n"/>
-      <c r="W33" s="11" t="n"/>
-      <c r="X33" s="11" t="n"/>
+      <c r="Q33" s="32" t="n">
+        <v>74.98999999999999</v>
+      </c>
+      <c r="R33" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S33" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T33" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U33" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V33" s="36" t="inlineStr">
+        <is>
+          <t>2% Bakuchiol extract, 100% organic squalane oil, Vitamin E</t>
+        </is>
+      </c>
+      <c r="W33" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X33" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y33" s="17" t="inlineStr">
         <is>
           <t>CAUTION (provisional)</t>
@@ -4900,12 +5979,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD33" s="15" t="n"/>
+      <c r="AD33" s="38" t="inlineStr">
+        <is>
+          <t>Only 3 ingredients, common names not INCI. 2% confirmed in title and ingredient block</t>
+        </is>
+      </c>
       <c r="AE33" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="34" ht="42" customHeight="1">
+    <row r="34" ht="58" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>1</v>
       </c>
@@ -4980,18 +6063,44 @@
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="11" t="n"/>
-      <c r="R34" s="11" t="n"/>
-      <c r="S34" s="11" t="n"/>
-      <c r="T34" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U34" s="11" t="n"/>
-      <c r="V34" s="11" t="n"/>
-      <c r="W34" s="11" t="n"/>
-      <c r="X34" s="11" t="n"/>
+      <c r="Q34" s="32" t="n">
+        <v>49</v>
+      </c>
+      <c r="R34" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S34" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T34" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U34" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V34" s="36" t="inlineStr">
+        <is>
+          <t>Water, Lactic Acid, Caprylic/Capric Triglyceride, Glycerin, Squalane, Prunus Amygdalus Dulcis (Sweet Almond) Oil, Simmondsia Chinensis (Jojoba) Seed Oil, Aloe Barbadensis Extract, Glyceryl Stearate, Stearic Acid, Polyacrylamide, Cetearyl Alcohol, C13-14 Isoparaffin, Cetyl Alcohol, Tocopherol, Laureth-7, Steareth-21, Xanthan Gum, Potassium Sorbate, Sodium Benzoate, Sodium Hydroxide, Citric Acid, Phenoxyethanol, Ethylhexylglycerin</t>
+        </is>
+      </c>
+      <c r="W34" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X34" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y34" s="17" t="inlineStr">
         <is>
           <t>CAUTION (provisional)</t>
@@ -5005,12 +6114,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD34" s="15" t="n"/>
+      <c r="AD34" s="38" t="inlineStr">
+        <is>
+          <t>10% appears in title; not restated in the INCI</t>
+        </is>
+      </c>
       <c r="AE34" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="35" ht="42" customHeight="1">
+    <row r="35" ht="58" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>1</v>
       </c>
@@ -5085,18 +6198,44 @@
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="11" t="n"/>
-      <c r="R35" s="11" t="n"/>
-      <c r="S35" s="11" t="n"/>
-      <c r="T35" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U35" s="11" t="n"/>
-      <c r="V35" s="11" t="n"/>
-      <c r="W35" s="11" t="n"/>
-      <c r="X35" s="11" t="n"/>
+      <c r="Q35" s="32" t="n">
+        <v>39</v>
+      </c>
+      <c r="R35" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S35" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T35" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U35" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V35" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, Lactic Acid, Glycerin, Cetearyl Alcohol, Cetyl Alcohol, Glyceryl Stearate, Carthamus Tinctorius (Safflower) Seed Oil, Avena Sativa Kernel Flour, Sodium Lauroyl Oat Amino Acids, Ceteareth-20, Sodium PCA, Avena Sativa Meal Extract, Avena Sativa Kernel Extract, Citrus Grandis (Grapefruit) Seed Extract, Ascorbyl Palmitate, Phospholipids, Phenoxyethanol, Hydroxypropyl Guar, Xanthan Gum, Ethylhexylglycerin, Sodium Phytate, Retinyl Palmitate, Tocopheryl Acetate</t>
+        </is>
+      </c>
+      <c r="W35" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X35" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y35" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -5104,18 +6243,26 @@
       </c>
       <c r="Z35" s="11" t="n"/>
       <c r="AA35" s="11" t="n"/>
-      <c r="AB35" s="11" t="n"/>
+      <c r="AB35" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Grapefruit Seed Extract (seed, not peel oil)</t>
+        </is>
+      </c>
       <c r="AC35" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD35" s="15" t="n"/>
+      <c r="AD35" s="38" t="inlineStr">
+        <is>
+          <t>Contains Retinyl Palmitate — relevant to pregnancy review</t>
+        </is>
+      </c>
       <c r="AE35" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="36" ht="42" customHeight="1">
+    <row r="36" ht="58" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>1</v>
       </c>
@@ -5190,18 +6337,44 @@
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="11" t="n"/>
-      <c r="R36" s="11" t="n"/>
-      <c r="S36" s="11" t="n"/>
-      <c r="T36" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U36" s="11" t="n"/>
-      <c r="V36" s="11" t="n"/>
-      <c r="W36" s="11" t="n"/>
-      <c r="X36" s="11" t="n"/>
+      <c r="Q36" s="32" t="n">
+        <v>39</v>
+      </c>
+      <c r="R36" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S36" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T36" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U36" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V36" s="36" t="inlineStr">
+        <is>
+          <t>100% Organic Squalane (Olive)</t>
+        </is>
+      </c>
+      <c r="W36" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="X36" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y36" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -5215,12 +6388,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD36" s="15" t="n"/>
+      <c r="AD36" s="38" t="inlineStr">
+        <is>
+          <t>Single-ingredient product. ECOCERT approved</t>
+        </is>
+      </c>
       <c r="AE36" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="37" ht="42" customHeight="1">
+    <row r="37" ht="58" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>1</v>
       </c>
@@ -5295,16 +6472,34 @@
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="11" t="n"/>
-      <c r="R37" s="11" t="n"/>
-      <c r="S37" s="11" t="n"/>
-      <c r="T37" s="12" t="inlineStr">
+      <c r="Q37" s="32" t="n">
+        <v>352</v>
+      </c>
+      <c r="R37" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S37" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T37" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U37" s="11" t="n"/>
-      <c r="V37" s="11" t="n"/>
+      <c r="U37" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V37" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W37" s="11" t="n"/>
       <c r="X37" s="11" t="n"/>
       <c r="Y37" s="13" t="inlineStr">
@@ -5320,12 +6515,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD37" s="15" t="n"/>
+      <c r="AD37" s="38" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
       <c r="AE37" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="38" ht="42" customHeight="1">
+    <row r="38" ht="58" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>1</v>
       </c>
@@ -5401,15 +6600,27 @@
       </c>
       <c r="P38" s="3" t="inlineStr"/>
       <c r="Q38" s="11" t="n"/>
-      <c r="R38" s="11" t="n"/>
+      <c r="R38" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
       <c r="S38" s="11" t="n"/>
-      <c r="T38" s="12" t="inlineStr">
+      <c r="T38" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U38" s="11" t="n"/>
-      <c r="V38" s="11" t="n"/>
+      <c r="U38" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="V38" s="43" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
       <c r="W38" s="11" t="n"/>
       <c r="X38" s="11" t="n"/>
       <c r="Y38" s="13" t="inlineStr">
@@ -5425,16 +6636,16 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="AD38" s="16" t="inlineStr">
-        <is>
-          <t>DOES NOT EXIST AS NAMED (Phase 9F): absent from the live Vitali catalogue. Do not substitute a near neighbour — re-identify or drop the row.</t>
+      <c r="AD38" s="39" t="inlineStr">
+        <is>
+          <t>DOES NOT EXIST AS NAMED (Phase 9F): absent from the live Vitali catalogue. Do not substitute a near neighbour — re-identify or drop the row. | CONFIRMED ABSENT 2026-09-04: verified three ways — not in /collections/all, not in /collections/bundles, not in the full 16-product products.json. The similarly named 'Copper Peptide Trio (Best Seller)' is a DIFFERENT product</t>
         </is>
       </c>
       <c r="AE38" s="14" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="42" customHeight="1">
+    <row r="39" ht="58" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>1</v>
       </c>
@@ -5509,16 +6720,34 @@
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="11" t="n"/>
-      <c r="R39" s="11" t="n"/>
-      <c r="S39" s="11" t="n"/>
-      <c r="T39" s="12" t="inlineStr">
+      <c r="Q39" s="32" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="R39" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S39" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T39" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U39" s="11" t="n"/>
-      <c r="V39" s="11" t="n"/>
+      <c r="U39" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V39" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W39" s="11" t="n"/>
       <c r="X39" s="11" t="n"/>
       <c r="Y39" s="13" t="inlineStr">
@@ -5534,12 +6763,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD39" s="15" t="n"/>
+      <c r="AD39" s="38" t="inlineStr">
+        <is>
+          <t>Bundle. Distinct from 'Advanced Copper Peptide Trio'</t>
+        </is>
+      </c>
       <c r="AE39" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="40" ht="42" customHeight="1">
+    <row r="40" ht="58" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>1</v>
       </c>
@@ -5614,16 +6847,34 @@
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="11" t="n"/>
-      <c r="R40" s="11" t="n"/>
-      <c r="S40" s="11" t="n"/>
-      <c r="T40" s="12" t="inlineStr">
+      <c r="Q40" s="32" t="n">
+        <v>215</v>
+      </c>
+      <c r="R40" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S40" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T40" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U40" s="11" t="n"/>
-      <c r="V40" s="11" t="n"/>
+      <c r="U40" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V40" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W40" s="11" t="n"/>
       <c r="X40" s="11" t="n"/>
       <c r="Y40" s="13" t="inlineStr">
@@ -5639,12 +6890,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD40" s="15" t="n"/>
+      <c r="AD40" s="38" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
       <c r="AE40" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="41" ht="42" customHeight="1">
+    <row r="41" ht="58" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>1</v>
       </c>
@@ -5719,16 +6974,34 @@
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="11" t="n"/>
-      <c r="R41" s="11" t="n"/>
-      <c r="S41" s="11" t="n"/>
-      <c r="T41" s="12" t="inlineStr">
+      <c r="Q41" s="32" t="n">
+        <v>229</v>
+      </c>
+      <c r="R41" s="33" t="inlineStr">
+        <is>
+          <t>https://www.vitaliskincare.com/pages/total-ingredients-list</t>
+        </is>
+      </c>
+      <c r="S41" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T41" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U41" s="11" t="n"/>
-      <c r="V41" s="11" t="n"/>
+      <c r="U41" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V41" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W41" s="11" t="n"/>
       <c r="X41" s="11" t="n"/>
       <c r="Y41" s="13" t="inlineStr">
@@ -5744,12 +7017,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD41" s="15" t="n"/>
+      <c r="AD41" s="38" t="inlineStr">
+        <is>
+          <t>Live title is 'Men's Essentials Set'. HIDDEN — absent from all collection pages, found only via products.json</t>
+        </is>
+      </c>
       <c r="AE41" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="42" ht="42" customHeight="1">
+    <row r="42" ht="58" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>1</v>
       </c>
@@ -5824,18 +7101,44 @@
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="11" t="n"/>
-      <c r="R42" s="11" t="n"/>
-      <c r="S42" s="11" t="n"/>
-      <c r="T42" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U42" s="11" t="n"/>
-      <c r="V42" s="11" t="n"/>
-      <c r="W42" s="11" t="n"/>
-      <c r="X42" s="11" t="n"/>
+      <c r="Q42" s="32" t="n">
+        <v>87</v>
+      </c>
+      <c r="R42" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S42" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T42" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U42" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V42" s="36" t="inlineStr">
+        <is>
+          <t>Organic Jojoba Oil, Organic Olive Oil, Organic Witch Hazel, Organic Rose Water, Organic Rosehip Oil, Organic Hemp Seed Oil, Marine Collagen, Organic Hawaiian Beeswax, CoQ10, Organic Bee Propolis, Astaxanthin (Microalgae), Organic Medicago Sativa (Alfalfa) Extract, Copper Tripeptide-1, Organic Neroli Oil, Organic Rose Otto Essential Oil, Organic Australian Sandalwood Essential Oil, Organic Frankincense Essential Oil, Organic Carrot Seed Essential Oil</t>
+        </is>
+      </c>
+      <c r="W42" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X42" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y42" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -5843,18 +7146,26 @@
       </c>
       <c r="Z42" s="11" t="n"/>
       <c r="AA42" s="11" t="n"/>
-      <c r="AB42" s="11" t="n"/>
+      <c r="AB42" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Neroli; Rose Otto EO; Sandalwood EO; Frankincense EO; Carrot Seed EO; Rose Water</t>
+        </is>
+      </c>
       <c r="AC42" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD42" s="15" t="n"/>
+      <c r="AD42" s="38" t="inlineStr">
+        <is>
+          <t>Common-name list, not strict INCI. 50ml $87 / 100ml $149</t>
+        </is>
+      </c>
       <c r="AE42" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="43" ht="42" customHeight="1">
+    <row r="43" ht="58" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>1</v>
       </c>
@@ -5929,16 +7240,34 @@
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="11" t="n"/>
-      <c r="R43" s="11" t="n"/>
-      <c r="S43" s="11" t="n"/>
-      <c r="T43" s="12" t="inlineStr">
+      <c r="Q43" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="R43" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S43" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T43" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U43" s="11" t="n"/>
-      <c r="V43" s="11" t="n"/>
+      <c r="U43" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="V43" s="43" t="inlineStr">
+        <is>
+          <t>NOT_PUBLISHED</t>
+        </is>
+      </c>
       <c r="W43" s="11" t="n"/>
       <c r="X43" s="11" t="n"/>
       <c r="Y43" s="13" t="inlineStr">
@@ -5954,12 +7283,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD43" s="15" t="n"/>
+      <c r="AD43" s="38" t="inlineStr">
+        <is>
+          <t>No labeled ingredient list — marketing '9 in 1 Formula' prose only. Claims 'formulated WITHOUT synthetic fragrances' but publishes no list to verify</t>
+        </is>
+      </c>
       <c r="AE43" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="44" ht="42" customHeight="1">
+    <row r="44" ht="58" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>1</v>
       </c>
@@ -6034,18 +7367,44 @@
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="11" t="n"/>
-      <c r="R44" s="11" t="n"/>
-      <c r="S44" s="11" t="n"/>
-      <c r="T44" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U44" s="11" t="n"/>
-      <c r="V44" s="11" t="n"/>
-      <c r="W44" s="11" t="n"/>
-      <c r="X44" s="11" t="n"/>
+      <c r="Q44" s="32" t="n">
+        <v>79</v>
+      </c>
+      <c r="R44" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S44" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T44" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U44" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V44" s="36" t="inlineStr">
+        <is>
+          <t>Water, Bamboo Stem Cell Extract, Glycerin, Diatomaceous Earth, Olive Glucoside, Niacinamide, Lactic Acid, Guar Gum, Papaver Somniferum Seeds, Leuconostoc/Radish Root Ferment Filtrate, Lactobacillus, Aloe Barbadensis Leaf Extract, Chondrus Crispus Extract, Hyaluronic Acid, Tremella Mushroom Extract, Betaine, Curcuma Longa Root Extract, Salix Alba (Willow) Bark Extract, Oryza Sativa (Rice) Extract, Morus Nigra Leaf Extract, Fulvic Acid, Madonna Lily Leaf Stem Cell Extract, Pomegranate Extract, Meteorite Powder, Mandelic Acid, Freshwater Pearl Powder, Montmorillonite, Citrus Limonum (Lemon) Peel Powder, Charcoal Powder, Amber Powder, Pacific Yew Branch Tip, Japanese Green Tea Powder, Citric Acid, Silver Ions, Prunus Avium (Cherry) Seed Powder, Olea Europaea (Olive) Seed Powder, Pinus Sylvestris (Pine) Oil, Cocos Nucifera Fruit Extract</t>
+        </is>
+      </c>
+      <c r="W44" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X44" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y44" s="17" t="inlineStr">
         <is>
           <t>CAUTION (provisional)</t>
@@ -6053,18 +7412,26 @@
       </c>
       <c r="Z44" s="11" t="n"/>
       <c r="AA44" s="11" t="n"/>
-      <c r="AB44" s="11" t="n"/>
+      <c r="AB44" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Pine Oil; Lemon Peel Powder</t>
+        </is>
+      </c>
       <c r="AC44" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD44" s="15" t="n"/>
+      <c r="AD44" s="38" t="inlineStr">
+        <is>
+          <t>60ml $79</t>
+        </is>
+      </c>
       <c r="AE44" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
+    <row r="45" ht="58" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>1</v>
       </c>
@@ -6139,18 +7506,44 @@
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="11" t="n"/>
-      <c r="R45" s="11" t="n"/>
-      <c r="S45" s="11" t="n"/>
-      <c r="T45" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U45" s="11" t="n"/>
-      <c r="V45" s="11" t="n"/>
-      <c r="W45" s="11" t="n"/>
-      <c r="X45" s="11" t="n"/>
+      <c r="Q45" s="32" t="n">
+        <v>55</v>
+      </c>
+      <c r="R45" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S45" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T45" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U45" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V45" s="36" t="inlineStr">
+        <is>
+          <t>Water/Aqua, Kaolin Clay, Geranium Flower Water, Rose Flower Water, Olive Oil, Sodium Olivoyl Glutamate, Leuconostoc/Radish Root Ferment Filtrate, Lactobacillus, Cocos Nucifera Fruit Extract, Pearl Powder, Vegetable Glycerin, Guar Gum, Tremella Mushroom Extract, Betaine, Wild Thyme, Horsetail, Marshmallow Root, Burdock Root, Gotu Kola, Eyebright, Giant Sea Kelp Extract, Panax Ginseng Root, Wild Yam Root, Green Coffee Seed, Laminaria Japonica Extract, Rosehip Seed Oil, Schizandra Fruit, Tocopherol, Colloidal Silver, Aloe Vera, Essential Oils (Geranium, Jasmine, Clary Sage, Roman Chamomile, Rose Damascena, Jojoba, Ylang Ylang)</t>
+        </is>
+      </c>
+      <c r="W45" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X45" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y45" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -6158,18 +7551,26 @@
       </c>
       <c r="Z45" s="11" t="n"/>
       <c r="AA45" s="11" t="n"/>
-      <c r="AB45" s="11" t="n"/>
+      <c r="AB45" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Geranium; Jasmine; Clary Sage; Roman Chamomile; Rose Damascena; Ylang Ylang EOs + geranium/rose waters</t>
+        </is>
+      </c>
       <c r="AC45" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD45" s="15" t="n"/>
+      <c r="AD45" s="38" t="inlineStr">
+        <is>
+          <t>Common-name list. 100ml $55</t>
+        </is>
+      </c>
       <c r="AE45" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="46" ht="42" customHeight="1">
+    <row r="46" ht="58" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>1</v>
       </c>
@@ -6244,18 +7645,44 @@
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="11" t="n"/>
-      <c r="R46" s="11" t="n"/>
-      <c r="S46" s="11" t="n"/>
-      <c r="T46" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U46" s="11" t="n"/>
-      <c r="V46" s="11" t="n"/>
-      <c r="W46" s="11" t="n"/>
-      <c r="X46" s="11" t="n"/>
+      <c r="Q46" s="32" t="n">
+        <v>55</v>
+      </c>
+      <c r="R46" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S46" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T46" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U46" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V46" s="36" t="inlineStr">
+        <is>
+          <t>Purified Hawaiian Water, Organic Extra Virgin Olive Oil, Organic Cocoa Butter, Organic Beeswax, Organic Evening Primrose Oil, Organic Aloe Vera Juice, Raw Organic Wilelaiki Honey, Organic Bee Propolis Extract, Organic Ylang Ylang Essential Oil, Organic Australian Sandalwood Essential Oil, Organic German Blue Chamomile Essential Oil, Organic Sea Buckthorn Essential Oil, Wildcrafted Calendula Essential Oil, Organic Carrot Seed Essential Oil, Wildcrafted Vanilla Essential Oil, Royal Jelly</t>
+        </is>
+      </c>
+      <c r="W46" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X46" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y46" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -6263,18 +7690,26 @@
       </c>
       <c r="Z46" s="11" t="n"/>
       <c r="AA46" s="11" t="n"/>
-      <c r="AB46" s="11" t="n"/>
+      <c r="AB46" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Ylang Ylang; Sandalwood; German Blue Chamomile; Sea Buckthorn; Calendula; Carrot Seed; Vanilla EOs</t>
+        </is>
+      </c>
       <c r="AC46" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD46" s="15" t="n"/>
+      <c r="AD46" s="38" t="inlineStr">
+        <is>
+          <t>Common-name list. 50ml $55 / 100ml $85</t>
+        </is>
+      </c>
       <c r="AE46" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="47" ht="42" customHeight="1">
+    <row r="47" ht="58" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>1</v>
       </c>
@@ -6349,18 +7784,44 @@
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr"/>
-      <c r="Q47" s="11" t="n"/>
-      <c r="R47" s="11" t="n"/>
-      <c r="S47" s="11" t="n"/>
-      <c r="T47" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U47" s="11" t="n"/>
-      <c r="V47" s="11" t="n"/>
-      <c r="W47" s="11" t="n"/>
-      <c r="X47" s="11" t="n"/>
+      <c r="Q47" s="32" t="n">
+        <v>85</v>
+      </c>
+      <c r="R47" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S47" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T47" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U47" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V47" s="36" t="inlineStr">
+        <is>
+          <t>Extra Virgin Olive Oil, Helichrysum Hydrosol, Hawaiian Beeswax, Pracaxi/Acai Oil blend, 10% Hyaluronic Acid (Vegan), Andiroba Oil, Leuconostoc/Radish Root Ferment Filtrate, Lactobacillus, Cocos Nucifera Fruit Extract, Buriti Oil, Raw Manuka Honey, Cacao Butter, Rose Hip Seed Oil, Royal Jelly, Edelweiss Stem Cells, Gardenia Stem Cells, Colostrum, CoQ10, Red Clover Extract, Chaga Mushroom Extract, Chlorella Extract, Camu Camu Extract, Schizandra Extract, Essential Oils (German Blue Chamomile, Madagascar Vanilla, Neroli, Lemon, Sea Buckthorn, Geranium)</t>
+        </is>
+      </c>
+      <c r="W47" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X47" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y47" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -6368,18 +7829,26 @@
       </c>
       <c r="Z47" s="11" t="n"/>
       <c r="AA47" s="11" t="n"/>
-      <c r="AB47" s="11" t="n"/>
+      <c r="AB47" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: German Blue Chamomile; Vanilla; Neroli; Lemon; Sea Buckthorn; Geranium EOs; Helichrysum</t>
+        </is>
+      </c>
       <c r="AC47" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD47" s="15" t="n"/>
+      <c r="AD47" s="38" t="inlineStr">
+        <is>
+          <t>Common-name list. 50ml $85</t>
+        </is>
+      </c>
       <c r="AE47" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="48" ht="42" customHeight="1">
+    <row r="48" ht="58" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>1</v>
       </c>
@@ -6454,18 +7923,44 @@
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr"/>
-      <c r="Q48" s="11" t="n"/>
-      <c r="R48" s="11" t="n"/>
-      <c r="S48" s="11" t="n"/>
-      <c r="T48" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U48" s="11" t="n"/>
-      <c r="V48" s="11" t="n"/>
-      <c r="W48" s="11" t="n"/>
-      <c r="X48" s="11" t="n"/>
+      <c r="Q48" s="32" t="n">
+        <v>55</v>
+      </c>
+      <c r="R48" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S48" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T48" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U48" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V48" s="36" t="inlineStr">
+        <is>
+          <t>Hawaiian Purified Water, Organic Witch Hazel Extract, Organic Rose Hydrosol, Organic Cane Alcohol, Caffeine, Niacinamide, Organic Olive Oil, Organic Rose Essential Oil, Organic Blood Orange Essential Oil, Organic Lemongrass Essential Oil, Organic Ylang Ylang Essential Oil, Organic Neroli Essential Oil, Flower of Saqqara Essential Oil, Nile Flower Essential Oil, Egyptian Myrrh Essential Oil, Blue Lotus Essential Oil</t>
+        </is>
+      </c>
+      <c r="W48" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X48" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y48" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -6473,18 +7968,26 @@
       </c>
       <c r="Z48" s="11" t="n"/>
       <c r="AA48" s="11" t="n"/>
-      <c r="AB48" s="11" t="n"/>
+      <c r="AB48" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: NINE essential oils: Rose, Blood Orange, Lemongrass, Ylang Ylang, Neroli, Flower of Saqqara, Nile Flower, Egyptian Myrrh, Blue Lotus + rose hydrosol</t>
+        </is>
+      </c>
       <c r="AC48" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD48" s="15" t="n"/>
+      <c r="AD48" s="38" t="inlineStr">
+        <is>
+          <t>Heaviest EO load in the catalog. Also contains cane alcohol. 100ml $55</t>
+        </is>
+      </c>
       <c r="AE48" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="49" ht="42" customHeight="1">
+    <row r="49" ht="58" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>1</v>
       </c>
@@ -6559,18 +8062,44 @@
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr"/>
-      <c r="Q49" s="11" t="n"/>
-      <c r="R49" s="11" t="n"/>
-      <c r="S49" s="11" t="n"/>
-      <c r="T49" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U49" s="11" t="n"/>
-      <c r="V49" s="11" t="n"/>
-      <c r="W49" s="11" t="n"/>
-      <c r="X49" s="11" t="n"/>
+      <c r="Q49" s="32" t="n">
+        <v>89</v>
+      </c>
+      <c r="R49" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S49" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T49" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U49" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V49" s="36" t="inlineStr">
+        <is>
+          <t>Organic Olive Oil, Purified Water, Organic Beeswax, Organic Brazilian Acai Butter, Organic Green Coffee Oil, Wildcrafted Andiroba Oil, Organic Rosehip Oil, Essential Oils (Australian Sandalwood, Madagascar Vanilla, Neroli, Ylang Ylang, Lemongrass)</t>
+        </is>
+      </c>
+      <c r="W49" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X49" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y49" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -6578,18 +8107,26 @@
       </c>
       <c r="Z49" s="11" t="n"/>
       <c r="AA49" s="11" t="n"/>
-      <c r="AB49" s="11" t="n"/>
+      <c r="AB49" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Sandalwood; Vanilla; Neroli; Ylang Ylang; Lemongrass EOs</t>
+        </is>
+      </c>
       <c r="AC49" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD49" s="15" t="n"/>
+      <c r="AD49" s="38" t="inlineStr">
+        <is>
+          <t>Common-name list. 200ml $89</t>
+        </is>
+      </c>
       <c r="AE49" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="50" ht="42" customHeight="1">
+    <row r="50" ht="58" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>1</v>
       </c>
@@ -6664,18 +8201,44 @@
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr"/>
-      <c r="Q50" s="11" t="n"/>
-      <c r="R50" s="11" t="n"/>
-      <c r="S50" s="11" t="n"/>
-      <c r="T50" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U50" s="11" t="n"/>
-      <c r="V50" s="11" t="n"/>
-      <c r="W50" s="11" t="n"/>
-      <c r="X50" s="11" t="n"/>
+      <c r="Q50" s="32" t="n">
+        <v>59</v>
+      </c>
+      <c r="R50" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S50" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T50" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U50" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V50" s="36" t="inlineStr">
+        <is>
+          <t>Helianthus Annuus Seed Oil, Simmondsia Chinensis Seed Oil, Babassu Oil, Pomegranate Oil, Tocopherol, Citrus Aurantium Bergamia Peel Oil (Bergamot), Myroxylon Pereirae Oil, Styrax Benzoin Resin Extract, Vanilla Planifolia Fruit Extract, Piper Nigrum Fruit Oil, Vetiveria Zizanoides Root Oil, Elettaria Cardamomum Oil, Amyris Balsamifera Bark Oil, Copaifera Species Resin Oils, Dipterocarpus Turbinatus Balsam Oil, Santalum Album Oil, Santalum Spicatum Wood Oil</t>
+        </is>
+      </c>
+      <c r="W50" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X50" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y50" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -6683,18 +8246,26 @@
       </c>
       <c r="Z50" s="11" t="n"/>
       <c r="AA50" s="11" t="n"/>
-      <c r="AB50" s="11" t="n"/>
+      <c r="AB50" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: 12 of 18 ingredients aromatic: Bergamot, Balsam Peru, Benzoin, Vanilla, Black Pepper, Vetiver, Cardamom, Amyris, Copaiba, Gurjun, Indian + Australian Sandalwood | EU allergen: Myroxylon Pereirae (Balsam of Peru) - major contact allergen</t>
+        </is>
+      </c>
       <c r="AC50" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD50" s="15" t="n"/>
+      <c r="AD50" s="38" t="inlineStr">
+        <is>
+          <t>Effectively a fragrance oil. 100ml $59</t>
+        </is>
+      </c>
       <c r="AE50" s="14" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="51" ht="42" customHeight="1">
+    <row r="51" ht="58" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>1</v>
       </c>
@@ -6769,16 +8340,34 @@
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr"/>
-      <c r="Q51" s="11" t="n"/>
-      <c r="R51" s="11" t="n"/>
-      <c r="S51" s="11" t="n"/>
-      <c r="T51" s="12" t="inlineStr">
+      <c r="Q51" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="R51" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S51" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T51" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U51" s="11" t="n"/>
-      <c r="V51" s="11" t="n"/>
+      <c r="U51" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="V51" s="43" t="inlineStr">
+        <is>
+          <t>NOT_PUBLISHED</t>
+        </is>
+      </c>
       <c r="W51" s="11" t="n"/>
       <c r="X51" s="11" t="n"/>
       <c r="Y51" s="17" t="inlineStr">
@@ -6794,9 +8383,9 @@
           <t>out_of_scope</t>
         </is>
       </c>
-      <c r="AD51" s="16" t="inlineStr">
-        <is>
-          <t>OUT OF SCOPE for the topical catalog: device/tool. Identity-only research.</t>
+      <c r="AD51" s="39" t="inlineStr">
+        <is>
+          <t>OUT OF SCOPE for the topical catalog: device/tool. Identity-only research. | Device/tool — no INCI expected</t>
         </is>
       </c>
       <c r="AE51" s="14" t="inlineStr">
@@ -6805,7 +8394,7 @@
         </is>
       </c>
     </row>
-    <row r="52" ht="42" customHeight="1">
+    <row r="52" ht="58" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>1</v>
       </c>
@@ -6880,16 +8469,34 @@
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr"/>
-      <c r="Q52" s="11" t="n"/>
-      <c r="R52" s="11" t="n"/>
-      <c r="S52" s="11" t="n"/>
-      <c r="T52" s="12" t="inlineStr">
+      <c r="Q52" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="R52" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S52" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T52" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U52" s="11" t="n"/>
-      <c r="V52" s="11" t="n"/>
+      <c r="U52" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="V52" s="43" t="inlineStr">
+        <is>
+          <t>NOT_PUBLISHED</t>
+        </is>
+      </c>
       <c r="W52" s="11" t="n"/>
       <c r="X52" s="11" t="n"/>
       <c r="Y52" s="13" t="inlineStr">
@@ -6905,12 +8512,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD52" s="15" t="n"/>
+      <c r="AD52" s="38" t="inlineStr">
+        <is>
+          <t>No labeled ingredient list — marketing '9 in 1 Formula' prose only. Sold only as multipacks; no single-unit price</t>
+        </is>
+      </c>
       <c r="AE52" s="14" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="53" ht="42" customHeight="1">
+    <row r="53" ht="58" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>1</v>
       </c>
@@ -6985,18 +8596,44 @@
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr"/>
-      <c r="Q53" s="11" t="n"/>
-      <c r="R53" s="11" t="n"/>
-      <c r="S53" s="11" t="n"/>
-      <c r="T53" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U53" s="11" t="n"/>
-      <c r="V53" s="11" t="n"/>
-      <c r="W53" s="11" t="n"/>
-      <c r="X53" s="11" t="n"/>
+      <c r="Q53" s="32" t="n">
+        <v>72</v>
+      </c>
+      <c r="R53" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S53" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T53" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U53" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V53" s="36" t="inlineStr">
+        <is>
+          <t>Organic Jojoba Oil, Organic Olive Oil, Organic Witch Hazel, Organic Rose Water, Organic Rosehip Oil, Organic Hemp Seed Oil, Marine Collagen, Organic Hawaiian Beeswax, CoQ10, Organic Bee Propolis, Astaxanthin, Organic Medicago Sativa (Alfalfa) Extract, Copper Tripeptide-1, Organic Neroli Oil, Organic Rose Otto Essential Oil, Organic Australian Sandalwood Essential Oil, Organic Frankincense Essential Oil, Organic Carrot Seed Essential Oil</t>
+        </is>
+      </c>
+      <c r="W53" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X53" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y53" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -7004,18 +8641,26 @@
       </c>
       <c r="Z53" s="11" t="n"/>
       <c r="AA53" s="11" t="n"/>
-      <c r="AB53" s="11" t="n"/>
+      <c r="AB53" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: Neroli; Rose Otto EO; Sandalwood EO; Frankincense EO; Carrot Seed EO; Rose Water</t>
+        </is>
+      </c>
       <c r="AC53" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD53" s="15" t="n"/>
+      <c r="AD53" s="38" t="inlineStr">
+        <is>
+          <t>Common-name list, not strict INCI. Only variant is 15ml 2-pack $72</t>
+        </is>
+      </c>
       <c r="AE53" s="14" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="54" ht="42" customHeight="1">
+    <row r="54" ht="58" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>1</v>
       </c>
@@ -7090,18 +8735,44 @@
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr"/>
-      <c r="Q54" s="11" t="n"/>
-      <c r="R54" s="11" t="n"/>
-      <c r="S54" s="11" t="n"/>
-      <c r="T54" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U54" s="11" t="n"/>
-      <c r="V54" s="11" t="n"/>
-      <c r="W54" s="11" t="n"/>
-      <c r="X54" s="11" t="n"/>
+      <c r="Q54" s="32" t="n">
+        <v>65</v>
+      </c>
+      <c r="R54" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S54" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T54" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U54" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V54" s="36" t="inlineStr">
+        <is>
+          <t>Extra Virgin Olive Oil, Helichrysum Hydrosol, Hawaiian Beeswax, Pracaxi/Acai Oil blend, 10% Hyaluronic Acid, Andiroba Oil, Leuconostoc/Radish Root Ferment Filtrate, Lactobacillus, Cocos Nucifera Fruit Extract, Buriti Oil, Raw Manuka Honey, Cacao Butter, Rose Hip Seed Oil, Royal Jelly, Edelweiss Stem Cells, Gardenia Stem Cells, Colostrum, CoQ10, Red Clover Extract, Chaga Mushroom Extract, Chlorella Extract, Camu Camu Extract, Schizandra Extract, Essential Oils (German Blue Chamomile, Madagascar Vanilla, Neroli, Lemon, Sea Buckthorn, Geranium)</t>
+        </is>
+      </c>
+      <c r="W54" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="X54" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y54" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -7109,18 +8780,26 @@
       </c>
       <c r="Z54" s="11" t="n"/>
       <c r="AA54" s="11" t="n"/>
-      <c r="AB54" s="11" t="n"/>
+      <c r="AB54" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: German Blue Chamomile; Vanilla; Neroli; Lemon; Sea Buckthorn; Geranium EOs; Helichrysum</t>
+        </is>
+      </c>
       <c r="AC54" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD54" s="15" t="n"/>
+      <c r="AD54" s="38" t="inlineStr">
+        <is>
+          <t>Only variant is 10ml 2-pack $65</t>
+        </is>
+      </c>
       <c r="AE54" s="14" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="55" ht="42" customHeight="1">
+    <row r="55" ht="58" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>1</v>
       </c>
@@ -7196,15 +8875,27 @@
       </c>
       <c r="P55" s="3" t="inlineStr"/>
       <c r="Q55" s="11" t="n"/>
-      <c r="R55" s="11" t="n"/>
+      <c r="R55" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
       <c r="S55" s="11" t="n"/>
-      <c r="T55" s="12" t="inlineStr">
+      <c r="T55" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U55" s="11" t="n"/>
-      <c r="V55" s="11" t="n"/>
+      <c r="U55" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
+      <c r="V55" s="43" t="inlineStr">
+        <is>
+          <t>NOT_FOUND</t>
+        </is>
+      </c>
       <c r="W55" s="11" t="n"/>
       <c r="X55" s="11" t="n"/>
       <c r="Y55" s="13" t="inlineStr">
@@ -7220,9 +8911,9 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="AD55" s="16" t="inlineStr">
-        <is>
-          <t>DOES NOT EXIST AS NAMED (Phase 9F): absent from the live Alitura catalogue. Do not substitute a near neighbour — re-identify or drop the row.</t>
+      <c r="AD55" s="39" t="inlineStr">
+        <is>
+          <t>DOES NOT EXIST AS NAMED (Phase 9F): absent from the live Alitura catalogue. Do not substitute a near neighbour — re-identify or drop the row. | CONFIRMED ABSENT 2026-09-04: all plausible handles 404; full 38-product feed shows only clay mask, gold serum and night cream travel packs. Re-identify or drop the row</t>
         </is>
       </c>
       <c r="AE55" s="14" t="inlineStr">
@@ -7231,7 +8922,7 @@
         </is>
       </c>
     </row>
-    <row r="56" ht="42" customHeight="1">
+    <row r="56" ht="58" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>1</v>
       </c>
@@ -7306,16 +8997,34 @@
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr"/>
-      <c r="Q56" s="11" t="n"/>
-      <c r="R56" s="11" t="n"/>
-      <c r="S56" s="11" t="n"/>
-      <c r="T56" s="12" t="inlineStr">
+      <c r="Q56" s="32" t="n">
+        <v>279</v>
+      </c>
+      <c r="R56" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S56" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T56" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U56" s="11" t="n"/>
-      <c r="V56" s="11" t="n"/>
+      <c r="U56" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V56" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W56" s="11" t="n"/>
       <c r="X56" s="11" t="n"/>
       <c r="Y56" s="13" t="inlineStr">
@@ -7331,12 +9040,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD56" s="15" t="n"/>
+      <c r="AD56" s="38" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
       <c r="AE56" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="57" ht="42" customHeight="1">
+    <row r="57" ht="58" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>1</v>
       </c>
@@ -7411,16 +9124,34 @@
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr"/>
-      <c r="Q57" s="11" t="n"/>
-      <c r="R57" s="11" t="n"/>
-      <c r="S57" s="11" t="n"/>
-      <c r="T57" s="12" t="inlineStr">
+      <c r="Q57" s="32" t="n">
+        <v>107</v>
+      </c>
+      <c r="R57" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S57" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T57" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U57" s="11" t="n"/>
-      <c r="V57" s="11" t="n"/>
+      <c r="U57" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V57" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W57" s="11" t="n"/>
       <c r="X57" s="11" t="n"/>
       <c r="Y57" s="13" t="inlineStr">
@@ -7436,12 +9167,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD57" s="15" t="n"/>
+      <c r="AD57" s="38" t="inlineStr">
+        <is>
+          <t>Bundle</t>
+        </is>
+      </c>
       <c r="AE57" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="58" ht="42" customHeight="1">
+    <row r="58" ht="58" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>1</v>
       </c>
@@ -7516,16 +9251,34 @@
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr"/>
-      <c r="Q58" s="11" t="n"/>
-      <c r="R58" s="11" t="n"/>
-      <c r="S58" s="11" t="n"/>
-      <c r="T58" s="12" t="inlineStr">
+      <c r="Q58" s="32" t="n">
+        <v>189</v>
+      </c>
+      <c r="R58" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S58" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T58" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U58" s="11" t="n"/>
-      <c r="V58" s="11" t="n"/>
+      <c r="U58" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V58" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W58" s="11" t="n"/>
       <c r="X58" s="11" t="n"/>
       <c r="Y58" s="13" t="inlineStr">
@@ -7541,12 +9294,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD58" s="15" t="n"/>
+      <c r="AD58" s="38" t="inlineStr">
+        <is>
+          <t>Bundle. URL handle is 'essentials-discovery-set'. A duplicate unlisted product exists at /products/the-ultimate-starter-set-copy, also $189</t>
+        </is>
+      </c>
       <c r="AE58" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="59" ht="42" customHeight="1">
+    <row r="59" ht="58" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>1</v>
       </c>
@@ -7621,16 +9378,34 @@
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr"/>
-      <c r="Q59" s="11" t="n"/>
-      <c r="R59" s="11" t="n"/>
-      <c r="S59" s="11" t="n"/>
-      <c r="T59" s="12" t="inlineStr">
+      <c r="Q59" s="32" t="n">
+        <v>165</v>
+      </c>
+      <c r="R59" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S59" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T59" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U59" s="11" t="n"/>
-      <c r="V59" s="11" t="n"/>
+      <c r="U59" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V59" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W59" s="11" t="n"/>
       <c r="X59" s="11" t="n"/>
       <c r="Y59" s="13" t="inlineStr">
@@ -7646,12 +9421,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD59" s="15" t="n"/>
+      <c r="AD59" s="38" t="inlineStr">
+        <is>
+          <t>Bundle incl. derma roller</t>
+        </is>
+      </c>
       <c r="AE59" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="60" ht="42" customHeight="1">
+    <row r="60" ht="58" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>1</v>
       </c>
@@ -7726,16 +9505,34 @@
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr"/>
-      <c r="Q60" s="11" t="n"/>
-      <c r="R60" s="11" t="n"/>
-      <c r="S60" s="11" t="n"/>
-      <c r="T60" s="12" t="inlineStr">
+      <c r="Q60" s="32" t="n">
+        <v>199</v>
+      </c>
+      <c r="R60" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S60" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T60" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U60" s="11" t="n"/>
-      <c r="V60" s="11" t="n"/>
+      <c r="U60" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V60" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W60" s="11" t="n"/>
       <c r="X60" s="11" t="n"/>
       <c r="Y60" s="13" t="inlineStr">
@@ -7751,12 +9548,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD60" s="15" t="n"/>
+      <c r="AD60" s="38" t="inlineStr">
+        <is>
+          <t>Bundle incl. derma roller</t>
+        </is>
+      </c>
       <c r="AE60" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="61" ht="42" customHeight="1">
+    <row r="61" ht="58" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>1</v>
       </c>
@@ -7831,16 +9632,34 @@
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr"/>
-      <c r="Q61" s="11" t="n"/>
-      <c r="R61" s="11" t="n"/>
-      <c r="S61" s="11" t="n"/>
-      <c r="T61" s="12" t="inlineStr">
+      <c r="Q61" s="32" t="n">
+        <v>315</v>
+      </c>
+      <c r="R61" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S61" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T61" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U61" s="11" t="n"/>
-      <c r="V61" s="11" t="n"/>
+      <c r="U61" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V61" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W61" s="11" t="n"/>
       <c r="X61" s="11" t="n"/>
       <c r="Y61" s="13" t="inlineStr">
@@ -7856,12 +9675,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD61" s="15" t="n"/>
+      <c r="AD61" s="38" t="inlineStr">
+        <is>
+          <t>Bundle. URL handle is 'the-alitura-skincare-collection'</t>
+        </is>
+      </c>
       <c r="AE61" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="62" ht="42" customHeight="1">
+    <row r="62" ht="58" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>1</v>
       </c>
@@ -7936,16 +9759,34 @@
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr"/>
-      <c r="Q62" s="11" t="n"/>
-      <c r="R62" s="11" t="n"/>
-      <c r="S62" s="11" t="n"/>
-      <c r="T62" s="12" t="inlineStr">
+      <c r="Q62" s="32" t="n">
+        <v>177</v>
+      </c>
+      <c r="R62" s="33" t="inlineStr">
+        <is>
+          <t>https://alitura.com</t>
+        </is>
+      </c>
+      <c r="S62" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T62" s="41" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U62" s="11" t="n"/>
-      <c r="V62" s="11" t="n"/>
+      <c r="U62" s="42" t="inlineStr">
+        <is>
+          <t>Not applicable - bundle</t>
+        </is>
+      </c>
+      <c r="V62" s="44" t="inlineStr">
+        <is>
+          <t>BUNDLE</t>
+        </is>
+      </c>
       <c r="W62" s="11" t="n"/>
       <c r="X62" s="11" t="n"/>
       <c r="Y62" s="13" t="inlineStr">
@@ -7961,12 +9802,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD62" s="15" t="n"/>
+      <c r="AD62" s="38" t="inlineStr">
+        <is>
+          <t>Bundle. Finish variants all $177</t>
+        </is>
+      </c>
       <c r="AE62" s="14" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="63" ht="42" customHeight="1">
+    <row r="63" ht="58" customHeight="1">
       <c r="A63" s="3" t="n">
         <v>2</v>
       </c>
@@ -8045,18 +9890,44 @@
           <t>Added as secondary expansion brand/product; confirm exact ingredient panel before using in production.</t>
         </is>
       </c>
-      <c r="Q63" s="11" t="n"/>
-      <c r="R63" s="11" t="n"/>
-      <c r="S63" s="11" t="n"/>
-      <c r="T63" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U63" s="11" t="n"/>
-      <c r="V63" s="11" t="n"/>
-      <c r="W63" s="11" t="n"/>
-      <c r="X63" s="11" t="n"/>
+      <c r="Q63" s="32" t="n">
+        <v>117</v>
+      </c>
+      <c r="R63" s="33" t="inlineStr">
+        <is>
+          <t>https://www.oneskin.co</t>
+        </is>
+      </c>
+      <c r="S63" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T63" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U63" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V63" s="36" t="inlineStr">
+        <is>
+          <t>Water, Glycerin, Sorbitan Olivate, Helianthus Annuus (Sunflower) Seed Oil, Squalane, Cetearyl Olivate, Carapa Guianensis Seed Oil, Vitis Vinifera (Grape) Seed Oil, Pentaclethra Macroloba Seed Oil, Rosa Canina Fruit Oil, Prunus Domestica Seed Oil, Calycophyllum Spruceanum Bark Extract, Caprylhydroxamic Acid, Glyceryl Caprylate, Decapeptide-52 (OS-01), Hyaluronic Acid, Sodium Hyaluronate, Sodium Hyaluronate Crosspolymer, Niacinamide, Allantoin, Bentonite, Tocopheryl Acetate, Cellulose, Cetyl Palmitate, Sorbitan Palmitate, Xanthan Gum, Potassium Sorbate, Phenoxyethanol, Sorbic Acid, Caprylyl Glycol, Tetrasodium Glutamate Diacetate</t>
+        </is>
+      </c>
+      <c r="W63" s="33" t="inlineStr">
+        <is>
+          <t>https://www.oneskin.co</t>
+        </is>
+      </c>
+      <c r="X63" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y63" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -8070,16 +9941,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD63" s="15" t="inlineStr">
-        <is>
-          <t>Needs product-page verification before app launch.</t>
+      <c r="AD63" s="38" t="inlineStr">
+        <is>
+          <t>Needs product-page verification before app launch. | Page states 'Formulated without fragrance'. One-time $117 / subscribe $100</t>
         </is>
       </c>
       <c r="AE63" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="64" ht="42" customHeight="1">
+    <row r="64" ht="58" customHeight="1">
       <c r="A64" s="3" t="n">
         <v>2</v>
       </c>
@@ -8158,18 +10029,44 @@
           <t>Added as secondary expansion brand/product; confirm exact ingredient panel before using in production.</t>
         </is>
       </c>
-      <c r="Q64" s="11" t="n"/>
-      <c r="R64" s="11" t="n"/>
-      <c r="S64" s="11" t="n"/>
-      <c r="T64" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U64" s="11" t="n"/>
-      <c r="V64" s="11" t="n"/>
-      <c r="W64" s="11" t="n"/>
-      <c r="X64" s="11" t="n"/>
+      <c r="Q64" s="32" t="n">
+        <v>109</v>
+      </c>
+      <c r="R64" s="33" t="inlineStr">
+        <is>
+          <t>https://www.oneskin.co</t>
+        </is>
+      </c>
+      <c r="S64" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T64" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U64" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V64" s="36" t="inlineStr">
+        <is>
+          <t>Water, Glycerin, Sorbitan Olivate, Squalane, Cetearyl Olivate, Butyrospermum Parkii (Shea) Butter, Simmondsia Chinensis (Jojoba) Seed Oil, Cystoseira Humilis Extract, d-Panthenol, Bentonite, Cetyl Palmitate, Sodium Hyaluronate Crosspolymer, Caprylhydroxamic Acid, Sorbitan Palmitate, Cellulose, Coffea Arabica Seedcake Extract, Allantoin, Fucus Vesiculosus Extract, Gluconolactone, Niacinamide, sh-Polypeptide-121, Sisymbrium Irio Seed Oil, Tocopheryl Acetate, Sorbic Acid, Caprylic/Capric Triglyceride, Ubiquinone, Lecithin, Decapeptide-52 (OS-01), Sodium Chloride, Maltodextrin, Acetyl Hexapeptide-8, Moringa Oleifera Seed Extract, Glyceryl Caprylate, Caprylyl Glycol, Tetrasodium Glutamate Diacetate, Alcohol, Sodium Benzoate, Phenoxyethanol, Xanthan Gum</t>
+        </is>
+      </c>
+      <c r="W64" s="33" t="inlineStr">
+        <is>
+          <t>https://www.oneskin.co</t>
+        </is>
+      </c>
+      <c r="X64" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y64" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -8183,16 +10080,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD64" s="15" t="inlineStr">
-        <is>
-          <t>Needs product-page verification before app launch.</t>
+      <c r="AD64" s="38" t="inlineStr">
+        <is>
+          <t>Needs product-page verification before app launch. | 'Fragrance Free' badge on page. 20 mL. Contains Alcohol</t>
         </is>
       </c>
       <c r="AE64" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="65" ht="42" customHeight="1">
+    <row r="65" ht="58" customHeight="1">
       <c r="A65" s="3" t="n">
         <v>2</v>
       </c>
@@ -8271,18 +10168,44 @@
           <t>Added as secondary expansion brand/product; confirm exact ingredient panel before using in production.</t>
         </is>
       </c>
-      <c r="Q65" s="11" t="n"/>
-      <c r="R65" s="11" t="n"/>
-      <c r="S65" s="11" t="n"/>
-      <c r="T65" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U65" s="11" t="n"/>
-      <c r="V65" s="11" t="n"/>
-      <c r="W65" s="11" t="n"/>
-      <c r="X65" s="11" t="n"/>
+      <c r="Q65" s="32" t="n">
+        <v>105</v>
+      </c>
+      <c r="R65" s="33" t="inlineStr">
+        <is>
+          <t>https://www.oneskin.co</t>
+        </is>
+      </c>
+      <c r="S65" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T65" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U65" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V65" s="36" t="inlineStr">
+        <is>
+          <t>Water, Glycerin, Limnanthes Alba (Meadowfoam) Seed Oil, Sorbitan Olivate, Squalane, Avena Sativa (Oat) Kernel Oil, Prunus Domestica Seed Oil, Cetearyl Olivate, Mangifera Indica (Mango) Seed Butter, Saccharide Isomerate, Panthenol, Tremella Fuciformis Sporocarp Extract, Tocopheryl Acetate, Decapeptide-52 (OS-01), Allantoin, Asiaticoside, Centella Asiatica Extract, Sodium Hyaluronate Crosspolymer, Ceramide NG, Galactoarabinan, Lepidium Sativum Sprout Extract, Soy Isoflavones, Niacinamide, Betaine, Bentonite, Cetyl Palmitate, Sorbitan Palmitate, Lecithin, Xanthan Gum, Polyglyceryl-10 Laurate, Polyglyceryl-6 Oleate, Sorbitan Oleate, Glyceryl Caprylate, Polysorbate 80, Alcohol, Caprylyl Glycol, Sorbic Acid, Caprylhydroxamic Acid, Tetrasodium Glutamate Diacetate, Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="W65" s="33" t="inlineStr">
+        <is>
+          <t>https://www.oneskin.co</t>
+        </is>
+      </c>
+      <c r="X65" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y65" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -8296,16 +10219,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD65" s="15" t="inlineStr">
-        <is>
-          <t>Needs product-page verification before app launch.</t>
+      <c r="AD65" s="38" t="inlineStr">
+        <is>
+          <t>Needs product-page verification before app launch. | 'Fragrance Free' badge. 250 mL. Contains Alcohol</t>
         </is>
       </c>
       <c r="AE65" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="66" ht="42" customHeight="1">
+    <row r="66" ht="58" customHeight="1">
       <c r="A66" s="3" t="n">
         <v>2</v>
       </c>
@@ -8384,18 +10307,44 @@
           <t>Added as secondary expansion brand/product; confirm exact ingredient panel before using in production.</t>
         </is>
       </c>
-      <c r="Q66" s="11" t="n"/>
-      <c r="R66" s="11" t="n"/>
-      <c r="S66" s="11" t="n"/>
-      <c r="T66" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U66" s="11" t="n"/>
-      <c r="V66" s="11" t="n"/>
-      <c r="W66" s="11" t="n"/>
-      <c r="X66" s="11" t="n"/>
+      <c r="Q66" s="32" t="n">
+        <v>57</v>
+      </c>
+      <c r="R66" s="33" t="inlineStr">
+        <is>
+          <t>https://www.oneskin.co</t>
+        </is>
+      </c>
+      <c r="S66" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T66" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U66" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V66" s="36" t="inlineStr">
+        <is>
+          <t>ACTIVE: Zinc Oxide 14%. INACTIVE: Caprylic/Capric Triglyceride, Butyloctyl Salicylate, C13-15 Alkane, Stearalkonium Hectorite, Coconut Alkanes, Euphorbia Cerifera (Candelilla) Wax, Helianthus Annuus Seed Wax, Propylene Carbonate, Quaternium-90 Bentonite, Butyrospermum Parkii Nut Extract, Decapeptide-52 (OS-01), Camellia Oleifera Seed Oil, Caesalpinia Spinosa Fruit Pod Extract, Helianthus Annuus Sprout Extract, Aloe Barbadensis Leaf Extract, Carthamus Tinctorius Seed Oil, Lactobacillus/Acerola Cherry Ferment, Coco-Caprylate/Caprate, Ceramide NP, Ceramide AP, Ceramide EOP, Ethylhexylglycerin, Caprylyl Glycol, Hexylene Glycol, Polyhydroxystearic Acid, Polyglyceryl-3 Polyricinoleate, Isostearic Acid, Lecithin, Phytosphingosine, Cholesterol, Sodium Lauroyl Lactylate, Carbomer, Xanthan Gum, Water, Propylene Glycol, Triethyl Citrate, Citric Acid, Sodium Benzoate, Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="W66" s="33" t="inlineStr">
+        <is>
+          <t>https://www.oneskin.co</t>
+        </is>
+      </c>
+      <c r="X66" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y66" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -8409,16 +10358,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD66" s="15" t="inlineStr">
-        <is>
-          <t>Needs product-page verification before app launch.</t>
+      <c r="AD66" s="38" t="inlineStr">
+        <is>
+          <t>Needs product-page verification before app launch. | SPF 30, NOT SPF 45. FULL OTC COMPLIANCE CONFIRMED: Drug Facts panel present, zinc 14% + Purpose stated, warnings present, broad-spectrum statement present. Best-documented sunscreen in the database</t>
         </is>
       </c>
       <c r="AE66" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="67" ht="42" customHeight="1">
+    <row r="67" ht="58" customHeight="1">
       <c r="A67" s="3" t="n">
         <v>2</v>
       </c>
@@ -8497,18 +10446,44 @@
           <t>Added as secondary expansion brand/product; confirm exact ingredient panel before using in production.</t>
         </is>
       </c>
-      <c r="Q67" s="11" t="n"/>
-      <c r="R67" s="11" t="n"/>
-      <c r="S67" s="11" t="n"/>
-      <c r="T67" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U67" s="11" t="n"/>
-      <c r="V67" s="11" t="n"/>
-      <c r="W67" s="11" t="n"/>
-      <c r="X67" s="11" t="n"/>
+      <c r="Q67" s="32" t="n">
+        <v>195</v>
+      </c>
+      <c r="R67" s="33" t="inlineStr">
+        <is>
+          <t>https://www.skinbetter.com</t>
+        </is>
+      </c>
+      <c r="S67" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T67" s="35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="U67" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V67" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, Butylene Glycol, Propanediol, Ethylhexyl Olivate, Cetearyl Alcohol, Chlorogenic Acids, Niacinamide, Lauryl Lactate, Dimethyl Isosorbide, Pyrroloquinoline Quinone Allyl Ester, Hydrolyzed Sodium Hyaluronate, Glycyrrhiza Glabra Root Extract, Tetrahexyldecyl Ascorbate, Ergothioneine, Taraxacum Officinale Root Extract, Arabidopsis Thaliana Extract, Carnosine, Camellia Sinensis Leaf Extract, Vitis Vinifera Seed Extract, Theobroma Cacao Seed Extract, Curcuma Longa Root Extract, Olea Europaea Fruit Extract, Euterpe Oleracea Fruit Extract, Palmitoyl Tripeptide-1, Buddleja Officinalis Flower Extract, Coffea Arabica Seed Extract, Crocus Sativus Flower Extract, Superoxide Dismutase, Ubiquinone, Plankton Extract, Micrococcus Lysate, Arginine, Zingiber Officinale Root Extract, Ceramide NP, Ceramide AP, Ceramide EOP, Linoleic Acid, Linolenic Acid, Ascorbic Acid, Bisabolol, Tocopherol, Tocopheryl Acetate, Cholesterol, Phytosphingosine, Jojoba Esters, Sodium PCA, Methyl Gluceth-20, Glycerin, Helianthus Annuus Seed Cera, Acacia Decurrens Flower Cera, Lecithin, Sodium Lauroyl Lactylate, Dicetyl Phosphate, Propanediol Dicaprylate/Caprate, Polyglycerin-3, Ceteth-20 Phosphate, Diisostearyl Malate, Xanthan Gum, Steareth-2, Acacia Senegal Gum, Carbomer, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Maltodextrin, Ricinoleth-40, Sodium Hydroxide, Citric Acid, Sodium Phytate, Ethylhexylglycerin, Phenoxyethanol, Ethylhexyl Palmitate, Alcohol, Lactic Acid, Pentylene Glycol, Sorbitan Isostearate, Tribehenin</t>
+        </is>
+      </c>
+      <c r="W67" s="33" t="inlineStr">
+        <is>
+          <t>https://www.skinbetter.com</t>
+        </is>
+      </c>
+      <c r="X67" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y67" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -8516,22 +10491,26 @@
       </c>
       <c r="Z67" s="11" t="n"/>
       <c r="AA67" s="11" t="n"/>
-      <c r="AB67" s="11" t="n"/>
+      <c r="AB67" s="37" t="inlineStr">
+        <is>
+          <t>Fragrant botanicals/EO: aromatic botanical extracts (turmeric, ginger, saffron, cocoa, coffee, buddleja) but no essential oils declared | EU allergen: Bisabolol present (not on EU-26 list)</t>
+        </is>
+      </c>
       <c r="AC67" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD67" s="15" t="inlineStr">
-        <is>
-          <t>Needs product-page verification before app launch.</t>
+      <c r="AD67" s="38" t="inlineStr">
+        <is>
+          <t>Needs product-page verification before app launch. | 30 ml $195; 50 ml also sold</t>
         </is>
       </c>
       <c r="AE67" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="68" ht="42" customHeight="1">
+    <row r="68" ht="58" customHeight="1">
       <c r="A68" s="3" t="n">
         <v>2</v>
       </c>
@@ -8610,18 +10589,44 @@
           <t>Added as secondary expansion brand/product; confirm exact ingredient panel before using in production.</t>
         </is>
       </c>
-      <c r="Q68" s="11" t="n"/>
-      <c r="R68" s="11" t="n"/>
-      <c r="S68" s="11" t="n"/>
-      <c r="T68" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U68" s="11" t="n"/>
-      <c r="V68" s="11" t="n"/>
-      <c r="W68" s="11" t="n"/>
-      <c r="X68" s="11" t="n"/>
+      <c r="Q68" s="32" t="n">
+        <v>145</v>
+      </c>
+      <c r="R68" s="33" t="inlineStr">
+        <is>
+          <t>https://www.skinbetter.com</t>
+        </is>
+      </c>
+      <c r="S68" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T68" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U68" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V68" s="36" t="inlineStr">
+        <is>
+          <t>Aqua, Sodium Glycolate, Glycolic Acid, Cetearyl Olivate, Pentylene Glycol, Cyclopentasiloxane, Isohexadecane, Sorbitan Olivate, Tetrahexyldecyl Ascorbate, Glycerin, Ceresin, Glycol Palmitate, Butylene Glycol, Niacinamide, Squalane, Methyl Gluceth-20, Ethyl Lactyl Retinoate, Palmitoyl Tripeptide-1, Palmitoyl Tetrapeptide-7, Ceramide NP, Hyaluronic Acid, Ubiquinone, Tocopherol, Bisabolol, Tocopheryl Acetate, Superoxide Dismutase, Butyrospermum Parkii (Shea) Butter, Allantoin, Glycyrrhetinic Acid, Sodium PCA, Panthenol, Camellia Sinensis Leaf Extract, Portulaca Oleracea Extract, Linoleic Acid, Cholesterol, Linolenic Acid, Magnesium Aluminum Silicate, Dimethyl Isosorbide, Dimethicone, Glyceryl Stearate, PEG-100 Stearate, Steareth-2, Hydroxyethylcellulose, Acacia Senegal Gum, Xanthan Gum, Hydrated Silica, Carbomer, Polysorbate 20, Disodium EDTA, Ethylhexylglycerin, Phenoxyethanol, Titanium Dioxide (CI 77891)</t>
+        </is>
+      </c>
+      <c r="W68" s="33" t="inlineStr">
+        <is>
+          <t>https://www.skinbetter.com</t>
+        </is>
+      </c>
+      <c r="X68" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y68" s="17" t="inlineStr">
         <is>
           <t>AVOID (provisional)</t>
@@ -8629,22 +10634,26 @@
       </c>
       <c r="Z68" s="11" t="n"/>
       <c r="AA68" s="11" t="n"/>
-      <c r="AB68" s="11" t="n"/>
+      <c r="AB68" s="37" t="inlineStr">
+        <is>
+          <t>EU allergen: Bisabolol present (not on EU-26 list)</t>
+        </is>
+      </c>
       <c r="AC68" s="14" t="inlineStr">
         <is>
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD68" s="15" t="inlineStr">
-        <is>
-          <t>Needs product-page verification before app launch.</t>
+      <c r="AD68" s="38" t="inlineStr">
+        <is>
+          <t>Needs product-page verification before app launch. | Contains Ethyl Lactyl Retinoate (retinoid) + glycolic acid. 30 ml $145</t>
         </is>
       </c>
       <c r="AE68" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="69" ht="42" customHeight="1">
+    <row r="69" ht="58" customHeight="1">
       <c r="A69" s="3" t="n">
         <v>2</v>
       </c>
@@ -8723,18 +10732,44 @@
           <t>Added as secondary expansion brand/product; confirm exact ingredient panel before using in production.</t>
         </is>
       </c>
-      <c r="Q69" s="11" t="n"/>
-      <c r="R69" s="11" t="n"/>
-      <c r="S69" s="11" t="n"/>
-      <c r="T69" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U69" s="11" t="n"/>
-      <c r="V69" s="11" t="n"/>
-      <c r="W69" s="11" t="n"/>
-      <c r="X69" s="11" t="n"/>
+      <c r="Q69" s="32" t="n">
+        <v>91</v>
+      </c>
+      <c r="R69" s="33" t="inlineStr">
+        <is>
+          <t>https://revisionskincare.com</t>
+        </is>
+      </c>
+      <c r="S69" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T69" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U69" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V69" s="36" t="inlineStr">
+        <is>
+          <t>ACTIVE: Titanium Dioxide 5.5%, Zinc Oxide 14.5%. INACTIVE: Water, Caprylic/Capric Triglyceride, Thermus Thermophilus Ferment, Polyglyceryl-2 Dipolyhydroxystearate, C12-15 Alkyl Benzoate, Dicaprylyl Carbonate, Cyclopentasiloxane, Dimethicone, Polyglyceryl-3 Diisostearate, Glycerin, Hydrogenated Starch Hydrolysate, Butylene Glycol, Aloe Barbadensis Leaf Juice, Betula Alba Bark Extract, Camellia Sinensis Leaf Extract, Plankton Extract, Beeswax, Acrylates/Dimethicone Copolymer, Squalane, Tocopheryl Acetate, Tetrahexyldecyl Ascorbate, Tocopherol, Palmitoyl Tripeptide-5, Dimethicone/Vinyl Dimethicone Crosspolymer, Lecithin, Palmitoyl Dipeptide-5 Diaminobutyroyl Hydroxythreonine, Leuconostoc/Radish Root Ferment Filtrate, Tetradecyl Aminobutyroylvalylaminobutyric Urea Acetate, Yeast Extract, Boron Nitride, Epigallocatechin Gallate, Ubiquinone, Simmondsia Chinensis Meal Extract, Melanin, Phenoxyethanol, Silica, Chlorphenesin, Polyhydroxystearic Acid, Xanthan Gum, Magnesium Chloride, Benzoic Acid, Sorbic Acid, Triethoxycaprylylsilane, Magnesium Sulfate, Iron Oxides</t>
+        </is>
+      </c>
+      <c r="W69" s="33" t="inlineStr">
+        <is>
+          <t>https://revisionskincare.com</t>
+        </is>
+      </c>
+      <c r="X69" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y69" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -8748,9 +10783,9 @@
           <t>blocked</t>
         </is>
       </c>
-      <c r="AD69" s="16" t="inlineStr">
-        <is>
-          <t>BLOCKER (Phase 9F): OTC sunscreen publishing no Drug Facts panel and no active percentages.</t>
+      <c r="AD69" s="39" t="inlineStr">
+        <is>
+          <t>BLOCKER (Phase 9F): OTC sunscreen publishing no Drug Facts panel and no active percentages. | PHASE 9F FINDING PARTLY CORRECTED 2026-09-04: active percentages ARE published (TiO2 5.5%, ZnO 14.5%) and a broad-spectrum statement IS present. Still MISSING: Drug Facts panel and Warnings. Page meta-description says SPF 50 while the product name says SPF 45 - internal inconsistency</t>
         </is>
       </c>
       <c r="AE69" s="14" t="inlineStr">
@@ -8759,7 +10794,7 @@
         </is>
       </c>
     </row>
-    <row r="70" ht="42" customHeight="1">
+    <row r="70" ht="58" customHeight="1">
       <c r="A70" s="3" t="n">
         <v>2</v>
       </c>
@@ -8838,18 +10873,44 @@
           <t>Added as secondary expansion brand/product; confirm exact ingredient panel before using in production.</t>
         </is>
       </c>
-      <c r="Q70" s="11" t="n"/>
-      <c r="R70" s="11" t="n"/>
-      <c r="S70" s="11" t="n"/>
-      <c r="T70" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="U70" s="11" t="n"/>
-      <c r="V70" s="11" t="n"/>
-      <c r="W70" s="11" t="n"/>
-      <c r="X70" s="11" t="n"/>
+      <c r="Q70" s="32" t="n">
+        <v>120</v>
+      </c>
+      <c r="R70" s="33" t="inlineStr">
+        <is>
+          <t>https://revisionskincare.com</t>
+        </is>
+      </c>
+      <c r="S70" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T70" s="40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="U70" s="34" t="inlineStr">
+        <is>
+          <t>Full INCI checked</t>
+        </is>
+      </c>
+      <c r="V70" s="36" t="inlineStr">
+        <is>
+          <t>Water, Tetrahexyldecyl Ascorbate, Pentylene Glycol, Dimethyl Isosorbide, Hydrolyzed Eruca Sativa Leaf, Glycerin, Zea Mays Starch, Hydrogenated Lecithin, Cetearyl Glucoside, Palmitoyl Glycine, Dimethicone, Acetyl Zingerone, Plantago Lanceolata Leaf Extract, Diglucosyl Gallic Acid, Squalane, Sodium Carboxymethyl Beta-Glucan, Euterpe Oleracea Fruit Extract, Ergothioneine, Punica Granatum Fruit Extract, Tocopherol, Ubiquinone, Acrylates/C10-30 Alkyl Acrylate Crosspolymer, Tromethamine, Undecane, Tridecane, Tocopheryl Acetate, Leuconostoc/Radish Root Ferment Filtrate, Phenoxyethanol, Disodium EDTA, PPG-12/SMDI Copolymer, Xanthan Gum, Citric Acid, Sodium Benzoate, Potassium Sorbate</t>
+        </is>
+      </c>
+      <c r="W70" s="33" t="inlineStr">
+        <is>
+          <t>https://revisionskincare.com</t>
+        </is>
+      </c>
+      <c r="X70" s="34" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
       <c r="Y70" s="13" t="inlineStr">
         <is>
           <t>Not reviewed</t>
@@ -8863,16 +10924,16 @@
           <t>research_only</t>
         </is>
       </c>
-      <c r="AD70" s="15" t="inlineStr">
-        <is>
-          <t>Needs product-page verification before app launch.</t>
+      <c r="AD70" s="38" t="inlineStr">
+        <is>
+          <t>Needs product-page verification before app launch. | Page carries a disclaimer that website ingredient lists may differ from packaging</t>
         </is>
       </c>
       <c r="AE70" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="71" ht="42" customHeight="1">
+    <row r="71" ht="58" customHeight="1">
       <c r="A71" s="3" t="n">
         <v>2</v>
       </c>
@@ -8959,7 +11020,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U71" s="11" t="n"/>
+      <c r="U71" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V71" s="11" t="n"/>
       <c r="W71" s="11" t="n"/>
       <c r="X71" s="11" t="n"/>
@@ -8978,14 +11043,14 @@
       </c>
       <c r="AD71" s="15" t="inlineStr">
         <is>
-          <t>Needs product-page verification before app launch.</t>
+          <t>Needs product-page verification before app launch. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE71" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="72" ht="42" customHeight="1">
+    <row r="72" ht="58" customHeight="1">
       <c r="A72" s="3" t="n">
         <v>2</v>
       </c>
@@ -9072,7 +11137,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U72" s="11" t="n"/>
+      <c r="U72" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V72" s="11" t="n"/>
       <c r="W72" s="11" t="n"/>
       <c r="X72" s="11" t="n"/>
@@ -9091,14 +11160,14 @@
       </c>
       <c r="AD72" s="15" t="inlineStr">
         <is>
-          <t>Needs product-page verification before app launch.</t>
+          <t>Needs product-page verification before app launch. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE72" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="73" ht="42" customHeight="1">
+    <row r="73" ht="58" customHeight="1">
       <c r="A73" s="3" t="n">
         <v>2</v>
       </c>
@@ -9185,7 +11254,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U73" s="11" t="n"/>
+      <c r="U73" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V73" s="11" t="n"/>
       <c r="W73" s="11" t="n"/>
       <c r="X73" s="11" t="n"/>
@@ -9204,14 +11277,14 @@
       </c>
       <c r="AD73" s="15" t="inlineStr">
         <is>
-          <t>Needs product-page verification before app launch.</t>
+          <t>Needs product-page verification before app launch. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE73" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="74" ht="42" customHeight="1">
+    <row r="74" ht="58" customHeight="1">
       <c r="A74" s="3" t="n">
         <v>2</v>
       </c>
@@ -9298,7 +11371,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U74" s="11" t="n"/>
+      <c r="U74" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V74" s="11" t="n"/>
       <c r="W74" s="11" t="n"/>
       <c r="X74" s="11" t="n"/>
@@ -9317,14 +11394,14 @@
       </c>
       <c r="AD74" s="15" t="inlineStr">
         <is>
-          <t>Needs product-page verification before app launch.</t>
+          <t>Needs product-page verification before app launch. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE74" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="75" ht="42" customHeight="1">
+    <row r="75" ht="58" customHeight="1">
       <c r="A75" s="3" t="n">
         <v>2</v>
       </c>
@@ -9411,7 +11488,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U75" s="11" t="n"/>
+      <c r="U75" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V75" s="11" t="n"/>
       <c r="W75" s="11" t="n"/>
       <c r="X75" s="11" t="n"/>
@@ -9430,14 +11511,14 @@
       </c>
       <c r="AD75" s="15" t="inlineStr">
         <is>
-          <t>Needs product-page verification before app launch.</t>
+          <t>Needs product-page verification before app launch. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE75" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="76" ht="42" customHeight="1">
+    <row r="76" ht="58" customHeight="1">
       <c r="A76" s="3" t="n">
         <v>2</v>
       </c>
@@ -9524,7 +11605,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U76" s="11" t="n"/>
+      <c r="U76" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V76" s="11" t="n"/>
       <c r="W76" s="11" t="n"/>
       <c r="X76" s="11" t="n"/>
@@ -9543,14 +11628,14 @@
       </c>
       <c r="AD76" s="15" t="inlineStr">
         <is>
-          <t>Needs product-page verification before app launch.</t>
+          <t>Needs product-page verification before app launch. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE76" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="77" ht="42" customHeight="1">
+    <row r="77" ht="58" customHeight="1">
       <c r="A77" s="3" t="n">
         <v>2</v>
       </c>
@@ -9637,7 +11722,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U77" s="11" t="n"/>
+      <c r="U77" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V77" s="11" t="n"/>
       <c r="W77" s="11" t="n"/>
       <c r="X77" s="11" t="n"/>
@@ -9656,14 +11745,14 @@
       </c>
       <c r="AD77" s="15" t="inlineStr">
         <is>
-          <t>Needs product-page verification before app launch.</t>
+          <t>Needs product-page verification before app launch. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE77" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="78" ht="42" customHeight="1">
+    <row r="78" ht="58" customHeight="1">
       <c r="A78" s="3" t="n">
         <v>2</v>
       </c>
@@ -9750,7 +11839,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U78" s="11" t="n"/>
+      <c r="U78" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V78" s="11" t="n"/>
       <c r="W78" s="11" t="n"/>
       <c r="X78" s="11" t="n"/>
@@ -9769,14 +11862,14 @@
       </c>
       <c r="AD78" s="15" t="inlineStr">
         <is>
-          <t>Needs product-page verification before app launch.</t>
+          <t>Needs product-page verification before app launch. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE78" s="14" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="79" ht="42" customHeight="1">
+    <row r="79" ht="58" customHeight="1">
       <c r="A79" s="3" t="n">
         <v>2</v>
       </c>
@@ -9863,7 +11956,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U79" s="11" t="n"/>
+      <c r="U79" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V79" s="11" t="n"/>
       <c r="W79" s="11" t="n"/>
       <c r="X79" s="11" t="n"/>
@@ -9882,7 +11979,7 @@
       </c>
       <c r="AD79" s="16" t="inlineStr">
         <is>
-          <t>OUT OF SCOPE for the topical catalog: device. Identity-only research; no label facts to capture.</t>
+          <t>OUT OF SCOPE for the topical catalog: device. Identity-only research; no label facts to capture. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE79" s="14" t="inlineStr">
@@ -9891,7 +11988,7 @@
         </is>
       </c>
     </row>
-    <row r="80" ht="42" customHeight="1">
+    <row r="80" ht="58" customHeight="1">
       <c r="A80" s="3" t="n">
         <v>2</v>
       </c>
@@ -9978,7 +12075,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U80" s="11" t="n"/>
+      <c r="U80" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V80" s="11" t="n"/>
       <c r="W80" s="11" t="n"/>
       <c r="X80" s="11" t="n"/>
@@ -9997,7 +12098,7 @@
       </c>
       <c r="AD80" s="16" t="inlineStr">
         <is>
-          <t>OUT OF SCOPE for the topical catalog: device. Identity-only research; no label facts to capture.</t>
+          <t>OUT OF SCOPE for the topical catalog: device. Identity-only research; no label facts to capture. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE80" s="14" t="inlineStr">
@@ -10006,7 +12107,7 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="42" customHeight="1">
+    <row r="81" ht="58" customHeight="1">
       <c r="A81" s="3" t="n">
         <v>2</v>
       </c>
@@ -10093,7 +12194,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U81" s="11" t="n"/>
+      <c r="U81" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V81" s="11" t="n"/>
       <c r="W81" s="11" t="n"/>
       <c r="X81" s="11" t="n"/>
@@ -10112,7 +12217,7 @@
       </c>
       <c r="AD81" s="16" t="inlineStr">
         <is>
-          <t>ROW MUST BE SPLIT (Phase 9F): one row covering two products with materially different panels — calcium present on one, absent on the other.</t>
+          <t>ROW MUST BE SPLIT (Phase 9F): one row covering two products with materially different panels — calcium present on one, absent on the other. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE81" s="14" t="inlineStr">
@@ -10121,7 +12226,7 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="42" customHeight="1">
+    <row r="82" ht="58" customHeight="1">
       <c r="A82" s="3" t="n">
         <v>2</v>
       </c>
@@ -10208,7 +12313,11 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="U82" s="11" t="n"/>
+      <c r="U82" s="42" t="inlineStr">
+        <is>
+          <t>Not checked</t>
+        </is>
+      </c>
       <c r="V82" s="11" t="n"/>
       <c r="W82" s="11" t="n"/>
       <c r="X82" s="11" t="n"/>
@@ -10227,7 +12336,7 @@
       </c>
       <c r="AD82" s="16" t="inlineStr">
         <is>
-          <t>OUT OF SCOPE: ingestible supplement. vAIne MVP excludes supplements.</t>
+          <t>OUT OF SCOPE: ingestible supplement. vAIne MVP excludes supplements. | SITE UNREACHABLE 2026-09-04: brand site timed out (likely bot protection). Needs a browser-based fetch to capture label data.</t>
         </is>
       </c>
       <c r="AE82" s="14" t="inlineStr">
